--- a/VerveStacks_MYS_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_MYS_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A84B72E7-AE78-4DD1-965F-6BED7CC3E06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97B4886F-8B0C-4C28-8D8C-1111EC770174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3847,7 +3847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBCA4F9-EBB7-41D9-A241-66975B3FC148}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CC8F0C-1037-46E3-A85E-B2CF841F6ED4}">
   <dimension ref="B9:H215"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -24098,7 +24098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D57DEE-4F66-46FA-8C39-98E937A0A6A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E0A671-08FB-443A-86CF-4137A0B2CDFB}">
   <dimension ref="B9:L215"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_MYS_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_MYS_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97B4886F-8B0C-4C28-8D8C-1111EC770174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F4FD01D-CED7-4E8E-8E6B-D1F4651E3FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6493" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6614" uniqueCount="1108">
   <si>
     <t>Unit</t>
   </si>
@@ -1963,6 +1963,27 @@
     <t>rez_spv_MYS_017</t>
   </si>
   <si>
+    <t>rez_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>rez_spv_MYS_024</t>
+  </si>
+  <si>
     <t>rez_won_MYS_001</t>
   </si>
   <si>
@@ -1981,6 +2002,18 @@
     <t>rez_won_MYS_006</t>
   </si>
   <si>
+    <t>rez_won_MYS_007</t>
+  </si>
+  <si>
+    <t>rez_won_MYS_008</t>
+  </si>
+  <si>
+    <t>rez_won_MYS_009</t>
+  </si>
+  <si>
+    <t>rez_won_MYS_010</t>
+  </si>
+  <si>
     <t>rez_wof_MYS_001</t>
   </si>
   <si>
@@ -2065,6 +2098,9 @@
     <t>Kalimantan Barat</t>
   </si>
   <si>
+    <t>Satun</t>
+  </si>
+  <si>
     <t>region_com</t>
   </si>
   <si>
@@ -2635,6 +2671,27 @@
     <t>elc_spv_MYS_017</t>
   </si>
   <si>
+    <t>elc_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_024</t>
+  </si>
+  <si>
     <t>elc_won_MYS_001</t>
   </si>
   <si>
@@ -2653,6 +2710,18 @@
     <t>elc_won_MYS_006</t>
   </si>
   <si>
+    <t>elc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_008</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_010</t>
+  </si>
+  <si>
     <t>elc_wof_MYS_001</t>
   </si>
   <si>
@@ -3259,6 +3328,27 @@
     <t>MYS-elc_spv_MYS_017</t>
   </si>
   <si>
+    <t>MYS-elc_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>MYS-elc_spv_MYS_024</t>
+  </si>
+  <si>
     <t>MYS-elc_won_MYS_001</t>
   </si>
   <si>
@@ -3275,6 +3365,18 @@
   </si>
   <si>
     <t>MYS-elc_won_MYS_006</t>
+  </si>
+  <si>
+    <t>MYS-elc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>MYS-elc_won_MYS_008</t>
+  </si>
+  <si>
+    <t>MYS-elc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>MYS-elc_won_MYS_010</t>
   </si>
   <si>
     <t>MYS-elc_wof_MYS_001</t>
@@ -3847,16 +3949,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CC8F0C-1037-46E3-A85E-B2CF841F6ED4}">
-  <dimension ref="B9:H215"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66ED5B81-520D-49E6-9200-1A0FCD2DF7C1}">
+  <dimension ref="B9:H226"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
       <c r="F9" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -3864,19 +3966,19 @@
         <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="D10" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="F10" t="s">
         <v>429</v>
       </c>
       <c r="G10" t="s">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="H10" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -3890,7 +3992,7 @@
         <v>116.1344488985544</v>
       </c>
       <c r="F11" t="s">
-        <v>869</v>
+        <v>892</v>
       </c>
       <c r="G11">
         <v>5.9288537445319918</v>
@@ -3910,7 +4012,7 @@
         <v>101.59595065726199</v>
       </c>
       <c r="F12" t="s">
-        <v>870</v>
+        <v>893</v>
       </c>
       <c r="G12">
         <v>2.9895220595413394</v>
@@ -3930,7 +4032,7 @@
         <v>101.72432489619833</v>
       </c>
       <c r="F13" t="s">
-        <v>871</v>
+        <v>894</v>
       </c>
       <c r="G13">
         <v>2.5946889385189822</v>
@@ -3950,7 +4052,7 @@
         <v>103.42559120686926</v>
       </c>
       <c r="F14" t="s">
-        <v>872</v>
+        <v>895</v>
       </c>
       <c r="G14">
         <v>1.7593842771057089</v>
@@ -3970,7 +4072,7 @@
         <v>103.4253147149402</v>
       </c>
       <c r="F15" t="s">
-        <v>873</v>
+        <v>896</v>
       </c>
       <c r="G15">
         <v>1.7595352988929214</v>
@@ -3990,7 +4092,7 @@
         <v>103.5368653481202</v>
       </c>
       <c r="F16" t="s">
-        <v>874</v>
+        <v>897</v>
       </c>
       <c r="G16">
         <v>1.3356948538343645</v>
@@ -4010,7 +4112,7 @@
         <v>110.34969548286465</v>
       </c>
       <c r="F17" t="s">
-        <v>875</v>
+        <v>898</v>
       </c>
       <c r="G17">
         <v>1.352574637693047</v>
@@ -4030,7 +4132,7 @@
         <v>110.30148943589188</v>
       </c>
       <c r="F18" t="s">
-        <v>876</v>
+        <v>899</v>
       </c>
       <c r="G18">
         <v>1.5594258027633334</v>
@@ -4050,7 +4152,7 @@
         <v>111.91876209557743</v>
       </c>
       <c r="F19" t="s">
-        <v>877</v>
+        <v>900</v>
       </c>
       <c r="G19">
         <v>2.2948212585724952</v>
@@ -4070,7 +4172,7 @@
         <v>113.42757402796822</v>
       </c>
       <c r="F20" t="s">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="G20">
         <v>3.3535904190689041</v>
@@ -4090,7 +4192,7 @@
         <v>101.72746745380093</v>
       </c>
       <c r="F21" t="s">
-        <v>879</v>
+        <v>902</v>
       </c>
       <c r="G21">
         <v>3.1226440167733487</v>
@@ -4110,7 +4212,7 @@
         <v>100.15781477963201</v>
       </c>
       <c r="F22" t="s">
-        <v>880</v>
+        <v>903</v>
       </c>
       <c r="G22">
         <v>6.3405912663202466</v>
@@ -4130,7 +4232,7 @@
         <v>100.28305742221175</v>
       </c>
       <c r="F23" t="s">
-        <v>881</v>
+        <v>904</v>
       </c>
       <c r="G23">
         <v>6.4881728024472611</v>
@@ -4150,7 +4252,7 @@
         <v>101.06914857559588</v>
       </c>
       <c r="F24" t="s">
-        <v>882</v>
+        <v>905</v>
       </c>
       <c r="G24">
         <v>4.4633800622615212</v>
@@ -4170,7 +4272,7 @@
         <v>102.12842825182091</v>
       </c>
       <c r="F25" t="s">
-        <v>883</v>
+        <v>906</v>
       </c>
       <c r="G25">
         <v>5.8139531420615134</v>
@@ -4190,7 +4292,7 @@
         <v>100.78876534195707</v>
       </c>
       <c r="F26" t="s">
-        <v>884</v>
+        <v>907</v>
       </c>
       <c r="G26">
         <v>4.3268830802413767</v>
@@ -4210,7 +4312,7 @@
         <v>100.78849054897424</v>
       </c>
       <c r="F27" t="s">
-        <v>885</v>
+        <v>908</v>
       </c>
       <c r="G27">
         <v>4.3270215549072937</v>
@@ -4230,7 +4332,7 @@
         <v>100.64371976231152</v>
       </c>
       <c r="F28" t="s">
-        <v>886</v>
+        <v>909</v>
       </c>
       <c r="G28">
         <v>4.1613271840848256</v>
@@ -4250,7 +4352,7 @@
         <v>101.13955751795064</v>
       </c>
       <c r="F29" t="s">
-        <v>887</v>
+        <v>910</v>
       </c>
       <c r="G29">
         <v>4.6911494890607557</v>
@@ -4270,7 +4372,7 @@
         <v>101.03169661691824</v>
       </c>
       <c r="F30" t="s">
-        <v>888</v>
+        <v>911</v>
       </c>
       <c r="G30">
         <v>4.5167471024399672</v>
@@ -4290,7 +4392,7 @@
         <v>111.87578098726937</v>
       </c>
       <c r="F31" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
       <c r="G31">
         <v>1.1459090780012822</v>
@@ -4310,7 +4412,7 @@
         <v>101.29696642049193</v>
       </c>
       <c r="F32" t="s">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="G32">
         <v>5.4090070644190016</v>
@@ -4330,7 +4432,7 @@
         <v>110.4387206908299</v>
       </c>
       <c r="F33" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
       <c r="G33">
         <v>1.4539636844848138</v>
@@ -4350,7 +4452,7 @@
         <v>100.35647532264908</v>
       </c>
       <c r="F34" t="s">
-        <v>892</v>
+        <v>915</v>
       </c>
       <c r="G34">
         <v>6.088248207179622</v>
@@ -4370,7 +4472,7 @@
         <v>117.79127890410496</v>
       </c>
       <c r="F35" t="s">
-        <v>893</v>
+        <v>916</v>
       </c>
       <c r="G35">
         <v>5.751809149638917</v>
@@ -4390,7 +4492,7 @@
         <v>101.92790599315728</v>
       </c>
       <c r="F36" t="s">
-        <v>894</v>
+        <v>917</v>
       </c>
       <c r="G36">
         <v>2.8828296878343922</v>
@@ -4410,7 +4512,7 @@
         <v>101.9276306995262</v>
       </c>
       <c r="F37" t="s">
-        <v>895</v>
+        <v>918</v>
       </c>
       <c r="G37">
         <v>2.8829731948111701</v>
@@ -4430,7 +4532,7 @@
         <v>103.36163346965982</v>
       </c>
       <c r="F38" t="s">
-        <v>896</v>
+        <v>919</v>
       </c>
       <c r="G38">
         <v>3.9753708172023359</v>
@@ -4450,7 +4552,7 @@
         <v>103.83818444798912</v>
       </c>
       <c r="F39" t="s">
-        <v>897</v>
+        <v>920</v>
       </c>
       <c r="G39">
         <v>1.5237467110011458</v>
@@ -4470,7 +4572,7 @@
         <v>101.5147675996849</v>
       </c>
       <c r="F40" t="s">
-        <v>898</v>
+        <v>921</v>
       </c>
       <c r="G40">
         <v>3.0505570116873391</v>
@@ -4490,7 +4592,7 @@
         <v>111.64954456926536</v>
       </c>
       <c r="F41" t="s">
-        <v>899</v>
+        <v>922</v>
       </c>
       <c r="G41">
         <v>1.1478145084251352</v>
@@ -4510,7 +4612,7 @@
         <v>112.34478620118158</v>
       </c>
       <c r="F42" t="s">
-        <v>900</v>
+        <v>923</v>
       </c>
       <c r="G42">
         <v>2.5518255691757115</v>
@@ -4530,7 +4632,7 @@
         <v>102.55512606356436</v>
       </c>
       <c r="F43" t="s">
-        <v>901</v>
+        <v>924</v>
       </c>
       <c r="G43">
         <v>2.1088086394786139</v>
@@ -4550,7 +4652,7 @@
         <v>100.50136834111331</v>
       </c>
       <c r="F44" t="s">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="G44">
         <v>5.7211942271187377</v>
@@ -4570,7 +4672,7 @@
         <v>101.5500739963111</v>
       </c>
       <c r="F45" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="G45">
         <v>2.836034629011368</v>
@@ -4590,7 +4692,7 @@
         <v>103.91862460020219</v>
       </c>
       <c r="F46" t="s">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="G46">
         <v>1.515428230436364</v>
@@ -4610,7 +4712,7 @@
         <v>113.34194121562304</v>
       </c>
       <c r="F47" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="G47">
         <v>3.5297847172803785</v>
@@ -4630,7 +4732,7 @@
         <v>101.53540794457037</v>
       </c>
       <c r="F48" t="s">
-        <v>906</v>
+        <v>929</v>
       </c>
       <c r="G48">
         <v>3.5015714608149811</v>
@@ -4650,7 +4752,7 @@
         <v>101.53513282592056</v>
       </c>
       <c r="F49" t="s">
-        <v>907</v>
+        <v>930</v>
       </c>
       <c r="G49">
         <v>3.5017133461856131</v>
@@ -4670,7 +4772,7 @@
         <v>114.05122498836997</v>
       </c>
       <c r="F50" t="s">
-        <v>908</v>
+        <v>931</v>
       </c>
       <c r="G50">
         <v>2.7731692067783902</v>
@@ -4690,7 +4792,7 @@
         <v>114.0347535756286</v>
       </c>
       <c r="F51" t="s">
-        <v>909</v>
+        <v>932</v>
       </c>
       <c r="G51">
         <v>4.47983166446868</v>
@@ -4710,7 +4812,7 @@
         <v>100.64738861076476</v>
       </c>
       <c r="F52" t="s">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="G52">
         <v>5.014020676718407</v>
@@ -4730,7 +4832,7 @@
         <v>100.5004042794816</v>
       </c>
       <c r="F53" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="G53">
         <v>5.7840922973576614</v>
@@ -4750,7 +4852,7 @@
         <v>100.62316004433698</v>
       </c>
       <c r="F54" t="s">
-        <v>912</v>
+        <v>935</v>
       </c>
       <c r="G54">
         <v>4.1792861767252774</v>
@@ -4770,7 +4872,7 @@
         <v>100.59077157467571</v>
       </c>
       <c r="F55" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="G55">
         <v>4.3909869074382852</v>
@@ -4790,7 +4892,7 @@
         <v>103.43411777371188</v>
       </c>
       <c r="F56" t="s">
-        <v>914</v>
+        <v>937</v>
       </c>
       <c r="G56">
         <v>4.290881340985603</v>
@@ -4810,7 +4912,7 @@
         <v>103.44903982401718</v>
       </c>
       <c r="F57" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="G57">
         <v>4.5964873649235392</v>
@@ -4830,7 +4932,7 @@
         <v>102.45115818038784</v>
       </c>
       <c r="F58" t="s">
-        <v>916</v>
+        <v>939</v>
       </c>
       <c r="G58">
         <v>5.9212229058880377</v>
@@ -4850,7 +4952,7 @@
         <v>102.50869320526796</v>
       </c>
       <c r="F59" t="s">
-        <v>917</v>
+        <v>940</v>
       </c>
       <c r="G59">
         <v>3.4758832155581336</v>
@@ -4870,7 +4972,7 @@
         <v>103.02186181507834</v>
       </c>
       <c r="F60" t="s">
-        <v>918</v>
+        <v>941</v>
       </c>
       <c r="G60">
         <v>1.8479654562366263</v>
@@ -4890,7 +4992,7 @@
         <v>102.16374433419961</v>
       </c>
       <c r="F61" t="s">
-        <v>919</v>
+        <v>942</v>
       </c>
       <c r="G61">
         <v>2.226598371549263</v>
@@ -4910,7 +5012,7 @@
         <v>102.05286268242671</v>
       </c>
       <c r="F62" t="s">
-        <v>920</v>
+        <v>943</v>
       </c>
       <c r="G62">
         <v>2.3490186761617502</v>
@@ -4930,7 +5032,7 @@
         <v>101.9622983287266</v>
       </c>
       <c r="F63" t="s">
-        <v>921</v>
+        <v>944</v>
       </c>
       <c r="G63">
         <v>2.5955737480972809</v>
@@ -4950,7 +5052,7 @@
         <v>102.00347449147468</v>
       </c>
       <c r="F64" t="s">
-        <v>922</v>
+        <v>945</v>
       </c>
       <c r="G64">
         <v>2.7335127909072354</v>
@@ -4970,7 +5072,7 @@
         <v>102.21294914318592</v>
       </c>
       <c r="F65" t="s">
-        <v>923</v>
+        <v>946</v>
       </c>
       <c r="G65">
         <v>2.3664761233042442</v>
@@ -4990,7 +5092,7 @@
         <v>100.63520702929893</v>
       </c>
       <c r="F66" t="s">
-        <v>924</v>
+        <v>947</v>
       </c>
       <c r="G66">
         <v>5.5911202948492287</v>
@@ -5010,7 +5112,7 @@
         <v>103.27390981924329</v>
       </c>
       <c r="F67" t="s">
-        <v>925</v>
+        <v>948</v>
       </c>
       <c r="G67">
         <v>3.8104122063946329</v>
@@ -5030,7 +5132,7 @@
         <v>111.68233662517976</v>
       </c>
       <c r="F68" t="s">
-        <v>926</v>
+        <v>949</v>
       </c>
       <c r="G68">
         <v>2.065825329684043</v>
@@ -5050,7 +5152,7 @@
         <v>113.31510319481504</v>
       </c>
       <c r="F69" t="s">
-        <v>927</v>
+        <v>950</v>
       </c>
       <c r="G69">
         <v>3.52753095983218</v>
@@ -5070,7 +5172,7 @@
         <v>115.8923330676744</v>
       </c>
       <c r="F70" t="s">
-        <v>928</v>
+        <v>951</v>
       </c>
       <c r="G70">
         <v>5.6486040497220014</v>
@@ -5090,7 +5192,7 @@
         <v>101.57591817979612</v>
       </c>
       <c r="F71" t="s">
-        <v>929</v>
+        <v>952</v>
       </c>
       <c r="G71">
         <v>4.4531653032154512</v>
@@ -5110,7 +5212,7 @@
         <v>110.14658076516127</v>
       </c>
       <c r="F72" t="s">
-        <v>930</v>
+        <v>953</v>
       </c>
       <c r="G72">
         <v>1.4626759504559332</v>
@@ -5130,7 +5232,7 @@
         <v>111.23571812692494</v>
       </c>
       <c r="F73" t="s">
-        <v>931</v>
+        <v>954</v>
       </c>
       <c r="G73">
         <v>1.1428416373732455</v>
@@ -5150,7 +5252,7 @@
         <v>113.11508121887664</v>
       </c>
       <c r="F74" t="s">
-        <v>932</v>
+        <v>955</v>
       </c>
       <c r="G74">
         <v>3.1501766244067069</v>
@@ -5170,7 +5272,7 @@
         <v>113.09254054390868</v>
       </c>
       <c r="F75" t="s">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="G75">
         <v>3.2866835058523582</v>
@@ -5190,7 +5292,7 @@
         <v>101.29096067362497</v>
       </c>
       <c r="F76" t="s">
-        <v>934</v>
+        <v>957</v>
       </c>
       <c r="G76">
         <v>4.2134361345784068</v>
@@ -5210,7 +5312,7 @@
         <v>101.85690604959844</v>
       </c>
       <c r="F77" t="s">
-        <v>935</v>
+        <v>958</v>
       </c>
       <c r="G77">
         <v>5.7423508729200821</v>
@@ -5230,7 +5332,7 @@
         <v>103.98274448549368</v>
       </c>
       <c r="F78" t="s">
-        <v>936</v>
+        <v>959</v>
       </c>
       <c r="G78">
         <v>1.4799615052240671</v>
@@ -5250,7 +5352,7 @@
         <v>103.05045626888098</v>
       </c>
       <c r="F79" t="s">
-        <v>937</v>
+        <v>960</v>
       </c>
       <c r="G79">
         <v>2.0773971142897576</v>
@@ -5270,7 +5372,7 @@
         <v>103.05018010042342</v>
       </c>
       <c r="F80" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="G80">
         <v>2.0775462759768613</v>
@@ -5290,7 +5392,7 @@
         <v>103.4608834304796</v>
       </c>
       <c r="F81" t="s">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="G81">
         <v>4.2625036419636828</v>
@@ -5310,7 +5412,7 @@
         <v>103.44927056742368</v>
       </c>
       <c r="F82" t="s">
-        <v>940</v>
+        <v>963</v>
       </c>
       <c r="G82">
         <v>4.2722398752272568</v>
@@ -5330,7 +5432,7 @@
         <v>100.37645751220352</v>
       </c>
       <c r="F83" t="s">
-        <v>941</v>
+        <v>964</v>
       </c>
       <c r="G83">
         <v>5.3736532099070544</v>
@@ -5350,7 +5452,7 @@
         <v>104.15989435032292</v>
       </c>
       <c r="F84" t="s">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="G84">
         <v>1.3971239894936665</v>
@@ -5370,7 +5472,7 @@
         <v>101.9231394230918</v>
       </c>
       <c r="F85" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="G85">
         <v>3.4727250864722849</v>
@@ -5390,7 +5492,7 @@
         <v>101.92286398821808</v>
       </c>
       <c r="F86" t="s">
-        <v>944</v>
+        <v>967</v>
       </c>
       <c r="G86">
         <v>3.4728691507706002</v>
@@ -5410,7 +5512,7 @@
         <v>102.6033619018408</v>
       </c>
       <c r="F87" t="s">
-        <v>945</v>
+        <v>968</v>
       </c>
       <c r="G87">
         <v>5.1514779830789861</v>
@@ -5430,7 +5532,7 @@
         <v>112.27101087041299</v>
       </c>
       <c r="F88" t="s">
-        <v>946</v>
+        <v>969</v>
       </c>
       <c r="G88">
         <v>2.1171485856935939</v>
@@ -5450,7 +5552,7 @@
         <v>103.41479661576147</v>
       </c>
       <c r="F89" t="s">
-        <v>947</v>
+        <v>970</v>
       </c>
       <c r="G89">
         <v>1.7007446636710222</v>
@@ -5470,7 +5572,7 @@
         <v>102.50348261166336</v>
       </c>
       <c r="F90" t="s">
-        <v>948</v>
+        <v>971</v>
       </c>
       <c r="G90">
         <v>2.7652011872870603</v>
@@ -5490,7 +5592,7 @@
         <v>102.50320683812572</v>
       </c>
       <c r="F91" t="s">
-        <v>949</v>
+        <v>972</v>
       </c>
       <c r="G91">
         <v>2.7653478774668554</v>
@@ -5510,7 +5612,7 @@
         <v>112.470820742215</v>
       </c>
       <c r="F92" t="s">
-        <v>950</v>
+        <v>973</v>
       </c>
       <c r="G92">
         <v>2.7364164292298958</v>
@@ -5530,7 +5632,7 @@
         <v>114.06081511584502</v>
       </c>
       <c r="F93" t="s">
-        <v>951</v>
+        <v>974</v>
       </c>
       <c r="G93">
         <v>2.9337076739900034</v>
@@ -5550,7 +5652,7 @@
         <v>113.38024307613216</v>
       </c>
       <c r="F94" t="s">
-        <v>952</v>
+        <v>975</v>
       </c>
       <c r="G94">
         <v>3.5508436537957548</v>
@@ -5570,7 +5672,7 @@
         <v>114.15988283925448</v>
       </c>
       <c r="F95" t="s">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="G95">
         <v>3.7296824984645873</v>
@@ -5590,7 +5692,7 @@
         <v>100.63647901864168</v>
       </c>
       <c r="F96" t="s">
-        <v>954</v>
+        <v>977</v>
       </c>
       <c r="G96">
         <v>4.3966624969855346</v>
@@ -5610,7 +5712,7 @@
         <v>115.53398761140784</v>
       </c>
       <c r="F97" t="s">
-        <v>955</v>
+        <v>978</v>
       </c>
       <c r="G97">
         <v>5.0082942304479419</v>
@@ -5630,7 +5732,7 @@
         <v>101.57083308923735</v>
       </c>
       <c r="F98" t="s">
-        <v>956</v>
+        <v>979</v>
       </c>
       <c r="G98">
         <v>3.0028729954066131</v>
@@ -5650,7 +5752,7 @@
         <v>101.56000643924716</v>
       </c>
       <c r="F99" t="s">
-        <v>957</v>
+        <v>980</v>
       </c>
       <c r="G99">
         <v>3.0590703600492035</v>
@@ -5670,7 +5772,7 @@
         <v>101.6661596</v>
       </c>
       <c r="F100" t="s">
-        <v>958</v>
+        <v>981</v>
       </c>
       <c r="G100">
         <v>3.1183862931022488</v>
@@ -5690,7 +5792,7 @@
         <v>101.6015570042094</v>
       </c>
       <c r="F101" t="s">
-        <v>959</v>
+        <v>982</v>
       </c>
       <c r="G101">
         <v>3.1148055178818104</v>
@@ -5710,7 +5812,7 @@
         <v>101.84574084860144</v>
       </c>
       <c r="F102" t="s">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="G102">
         <v>3.3673187438990704</v>
@@ -5730,7 +5832,7 @@
         <v>101.6831605661328</v>
       </c>
       <c r="F103" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="G103">
         <v>3.2668046436111378</v>
@@ -5750,7 +5852,7 @@
         <v>101.77171794980714</v>
       </c>
       <c r="F104" t="s">
-        <v>962</v>
+        <v>985</v>
       </c>
       <c r="G104">
         <v>2.937542543629605</v>
@@ -5770,7 +5872,7 @@
         <v>103.58523818346885</v>
       </c>
       <c r="F105" t="s">
-        <v>963</v>
+        <v>986</v>
       </c>
       <c r="G105">
         <v>1.4854632420680494</v>
@@ -5790,7 +5892,7 @@
         <v>101.64833607541678</v>
       </c>
       <c r="F106" t="s">
-        <v>964</v>
+        <v>987</v>
       </c>
       <c r="G106">
         <v>2.7988372074083752</v>
@@ -5810,7 +5912,7 @@
         <v>101.75664789598648</v>
       </c>
       <c r="F107" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
       <c r="G107">
         <v>2.7999620654733528</v>
@@ -5830,7 +5932,7 @@
         <v>101.57593026145013</v>
       </c>
       <c r="F108" t="s">
-        <v>966</v>
+        <v>989</v>
       </c>
       <c r="G108">
         <v>2.8466565585112562</v>
@@ -5850,7 +5952,7 @@
         <v>101.60121828580394</v>
       </c>
       <c r="F109" t="s">
-        <v>967</v>
+        <v>990</v>
       </c>
       <c r="G109">
         <v>3.1967487519492925</v>
@@ -5870,7 +5972,7 @@
         <v>101.65703770000002</v>
       </c>
       <c r="F110" t="s">
-        <v>968</v>
+        <v>991</v>
       </c>
       <c r="G110">
         <v>3.1892250929491097</v>
@@ -5890,7 +5992,7 @@
         <v>101.46837169932012</v>
       </c>
       <c r="F111" t="s">
-        <v>969</v>
+        <v>992</v>
       </c>
       <c r="G111">
         <v>3.0413562205164872</v>
@@ -5910,7 +6012,7 @@
         <v>101.4855886</v>
       </c>
       <c r="F112" t="s">
-        <v>970</v>
+        <v>993</v>
       </c>
       <c r="G112">
         <v>3.0242392933061262</v>
@@ -5930,7 +6032,7 @@
         <v>101.3151061899045</v>
       </c>
       <c r="F113" t="s">
-        <v>971</v>
+        <v>994</v>
       </c>
       <c r="G113">
         <v>3.1525832416981521</v>
@@ -5950,7 +6052,7 @@
         <v>101.315381016933</v>
       </c>
       <c r="F114" t="s">
-        <v>972</v>
+        <v>995</v>
       </c>
       <c r="G114">
         <v>3.1524429546177166</v>
@@ -5970,7 +6072,7 @@
         <v>101.441692599953</v>
       </c>
       <c r="F115" t="s">
-        <v>973</v>
+        <v>996</v>
       </c>
       <c r="G115">
         <v>3.1050905933456701</v>
@@ -5990,7 +6092,7 @@
         <v>101.50610930000001</v>
       </c>
       <c r="F116" t="s">
-        <v>974</v>
+        <v>997</v>
       </c>
       <c r="G116">
         <v>3.0930466931571181</v>
@@ -6010,7 +6112,7 @@
         <v>101.57845932153492</v>
       </c>
       <c r="F117" t="s">
-        <v>975</v>
+        <v>998</v>
       </c>
       <c r="G117">
         <v>3.3101982041012441</v>
@@ -6030,7 +6132,7 @@
         <v>101.68274544579188</v>
       </c>
       <c r="F118" t="s">
-        <v>976</v>
+        <v>999</v>
       </c>
       <c r="G118">
         <v>2.9656314334963128</v>
@@ -6050,7 +6152,7 @@
         <v>101.57620523476568</v>
       </c>
       <c r="F119" t="s">
-        <v>977</v>
+        <v>1000</v>
       </c>
       <c r="G119">
         <v>2.8465150960002061</v>
@@ -6070,7 +6172,7 @@
         <v>101.69608949911068</v>
       </c>
       <c r="F120" t="s">
-        <v>978</v>
+        <v>1001</v>
       </c>
       <c r="G120">
         <v>5.6490482886149254</v>
@@ -6090,7 +6192,7 @@
         <v>103.65709987655066</v>
       </c>
       <c r="F121" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="G121">
         <v>1.5514824532558715</v>
@@ -6110,7 +6212,7 @@
         <v>103.55512589808438</v>
       </c>
       <c r="F122" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="G122">
         <v>1.3674830980265056</v>
@@ -6130,7 +6232,7 @@
         <v>103.6725641623748</v>
       </c>
       <c r="F123" t="s">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="G123">
         <v>1.4940231929570378</v>
@@ -6150,7 +6252,7 @@
         <v>103.83586875712844</v>
       </c>
       <c r="F124" t="s">
-        <v>982</v>
+        <v>1005</v>
       </c>
       <c r="G124">
         <v>1.5051397313315522</v>
@@ -6170,7 +6272,7 @@
         <v>103.5365887628774</v>
       </c>
       <c r="F125" t="s">
-        <v>983</v>
+        <v>1006</v>
       </c>
       <c r="G125">
         <v>1.3358460948622837</v>
@@ -6190,7 +6292,7 @@
         <v>100.89358957528808</v>
       </c>
       <c r="F126" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
       <c r="G126">
         <v>4.7946625899688744</v>
@@ -6210,7 +6312,7 @@
         <v>101.75954099656614</v>
       </c>
       <c r="F127" t="s">
-        <v>985</v>
+        <v>1008</v>
       </c>
       <c r="G127">
         <v>2.9411457457178809</v>
@@ -6230,7 +6332,7 @@
         <v>101.80052852735432</v>
       </c>
       <c r="F128" t="s">
-        <v>986</v>
+        <v>1009</v>
       </c>
       <c r="G128">
         <v>2.554439461711949</v>
@@ -6250,7 +6352,7 @@
         <v>101.79214090449062</v>
       </c>
       <c r="F129" t="s">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="G129">
         <v>2.5307397930242721</v>
@@ -6270,7 +6372,7 @@
         <v>102.16342160847036</v>
       </c>
       <c r="F130" t="s">
-        <v>988</v>
+        <v>1011</v>
       </c>
       <c r="G130">
         <v>5.7233308436258961</v>
@@ -6290,7 +6392,7 @@
         <v>102.60621239586776</v>
       </c>
       <c r="F131" t="s">
-        <v>989</v>
+        <v>1012</v>
       </c>
       <c r="G131">
         <v>5.1667736607362063</v>
@@ -6310,7 +6412,7 @@
         <v>100.28679302615996</v>
       </c>
       <c r="F132" t="s">
-        <v>990</v>
+        <v>1013</v>
       </c>
       <c r="G132">
         <v>6.4091944948210511</v>
@@ -6330,7 +6432,7 @@
         <v>100.45699334502896</v>
       </c>
       <c r="F133" t="s">
-        <v>991</v>
+        <v>1014</v>
       </c>
       <c r="G133">
         <v>5.2679228303574508</v>
@@ -6350,7 +6452,7 @@
         <v>100.41302091323628</v>
       </c>
       <c r="F134" t="s">
-        <v>992</v>
+        <v>1015</v>
       </c>
       <c r="G134">
         <v>5.3133038721952364</v>
@@ -6370,7 +6472,7 @@
         <v>100.54116964773505</v>
       </c>
       <c r="F135" t="s">
-        <v>993</v>
+        <v>1016</v>
       </c>
       <c r="G135">
         <v>5.2885907266462624</v>
@@ -6390,7 +6492,7 @@
         <v>101.3563201</v>
       </c>
       <c r="F136" t="s">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="G136">
         <v>5.5514787880079233</v>
@@ -6410,7 +6512,7 @@
         <v>101.54606537677375</v>
       </c>
       <c r="F137" t="s">
-        <v>995</v>
+        <v>1018</v>
       </c>
       <c r="G137">
         <v>3.4210439832580124</v>
@@ -6430,7 +6532,7 @@
         <v>101.32347797869971</v>
       </c>
       <c r="F138" t="s">
-        <v>996</v>
+        <v>1019</v>
       </c>
       <c r="G138">
         <v>3.1180558062958177</v>
@@ -6450,7 +6552,7 @@
         <v>101.69362662933533</v>
       </c>
       <c r="F139" t="s">
-        <v>997</v>
+        <v>1020</v>
       </c>
       <c r="G139">
         <v>3.2136227843272978</v>
@@ -6470,7 +6572,7 @@
         <v>100.40898491485623</v>
       </c>
       <c r="F140" t="s">
-        <v>998</v>
+        <v>1021</v>
       </c>
       <c r="G140">
         <v>5.3753778538715116</v>
@@ -6490,7 +6592,7 @@
         <v>100.53282709993954</v>
       </c>
       <c r="F141" t="s">
-        <v>999</v>
+        <v>1022</v>
       </c>
       <c r="G141">
         <v>5.8101637877043935</v>
@@ -6510,7 +6612,7 @@
         <v>100.605935</v>
       </c>
       <c r="F142" t="s">
-        <v>1000</v>
+        <v>1023</v>
       </c>
       <c r="G142">
         <v>5.0091561891095484</v>
@@ -6530,7 +6632,7 @@
         <v>103.80646779999999</v>
       </c>
       <c r="F143" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="G143">
         <v>1.4806425966970858</v>
@@ -6550,7 +6652,7 @@
         <v>101.85703749999998</v>
       </c>
       <c r="F144" t="s">
-        <v>1002</v>
+        <v>1025</v>
       </c>
       <c r="G144">
         <v>3.2082182929081</v>
@@ -6570,7 +6672,7 @@
         <v>101.7404738</v>
       </c>
       <c r="F145" t="s">
-        <v>1003</v>
+        <v>1026</v>
       </c>
       <c r="G145">
         <v>3.1462013930420967</v>
@@ -6590,7 +6692,7 @@
         <v>101.6452814</v>
       </c>
       <c r="F146" t="s">
-        <v>1004</v>
+        <v>1027</v>
       </c>
       <c r="G146">
         <v>2.851926793680398</v>
@@ -6610,7 +6712,7 @@
         <v>111.56507999996708</v>
       </c>
       <c r="F147" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="G147">
         <v>1.4459435969518697</v>
@@ -6630,7 +6732,7 @@
         <v>114.29569979705522</v>
       </c>
       <c r="F148" t="s">
-        <v>1006</v>
+        <v>1029</v>
       </c>
       <c r="G148">
         <v>2.6708031956313887</v>
@@ -6650,7 +6752,7 @@
         <v>100.60573879999998</v>
       </c>
       <c r="F149" t="s">
-        <v>1007</v>
+        <v>1030</v>
       </c>
       <c r="G149">
         <v>5.0188902890896134</v>
@@ -6670,7 +6772,7 @@
         <v>101.06916374978988</v>
       </c>
       <c r="F150" t="s">
-        <v>1008</v>
+        <v>1031</v>
       </c>
       <c r="G150">
         <v>5.2323709393337268</v>
@@ -6690,7 +6792,7 @@
         <v>103.20206434610044</v>
       </c>
       <c r="F151" t="s">
-        <v>1009</v>
+        <v>1032</v>
       </c>
       <c r="G151">
         <v>1.9850659994565047</v>
@@ -6710,7 +6812,7 @@
         <v>101.09648989355983</v>
       </c>
       <c r="F152" t="s">
-        <v>1010</v>
+        <v>1033</v>
       </c>
       <c r="G152">
         <v>5.2165895020145934</v>
@@ -6730,7 +6832,7 @@
         <v>101.20864446852885</v>
       </c>
       <c r="F153" t="s">
-        <v>1011</v>
+        <v>1034</v>
       </c>
       <c r="G153">
         <v>5.4308438052133416</v>
@@ -6750,7 +6852,7 @@
         <v>101.21461699837732</v>
       </c>
       <c r="F154" t="s">
-        <v>1012</v>
+        <v>1035</v>
       </c>
       <c r="G154">
         <v>5.4365235969222425</v>
@@ -6770,7 +6872,7 @@
         <v>101.57873442171856</v>
       </c>
       <c r="F155" t="s">
-        <v>1013</v>
+        <v>1036</v>
       </c>
       <c r="G155">
         <v>3.3100562622515661</v>
@@ -6790,7 +6892,7 @@
         <v>104.17430406297591</v>
       </c>
       <c r="F156" t="s">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="G156">
         <v>1.3790542732276749</v>
@@ -6810,7 +6912,7 @@
         <v>103.60708239999995</v>
       </c>
       <c r="F157" t="s">
-        <v>1015</v>
+        <v>1038</v>
       </c>
       <c r="G157">
         <v>1.4818544966944165</v>
@@ -6830,7 +6932,7 @@
         <v>101.94756459999996</v>
       </c>
       <c r="F158" t="s">
-        <v>1016</v>
+        <v>1039</v>
       </c>
       <c r="G158">
         <v>3.478042592327192</v>
@@ -6850,7 +6952,7 @@
         <v>101.73656119999998</v>
       </c>
       <c r="F159" t="s">
-        <v>1017</v>
+        <v>1040</v>
       </c>
       <c r="G159">
         <v>2.6038096942214053</v>
@@ -6870,7 +6972,7 @@
         <v>113.46815919999996</v>
       </c>
       <c r="F160" t="s">
-        <v>1018</v>
+        <v>1041</v>
       </c>
       <c r="G160">
         <v>3.3762988925458184</v>
@@ -6890,7 +6992,7 @@
         <v>111.54916434520432</v>
       </c>
       <c r="F161" t="s">
-        <v>1019</v>
+        <v>1042</v>
       </c>
       <c r="G161">
         <v>1.4895594509742749</v>
@@ -6910,7 +7012,7 @@
         <v>103.4693912</v>
       </c>
       <c r="F162" t="s">
-        <v>1020</v>
+        <v>1043</v>
       </c>
       <c r="G162">
         <v>1.452472496759613</v>
@@ -6930,7 +7032,7 @@
         <v>103.75362935792778</v>
       </c>
       <c r="F163" t="s">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="G163">
         <v>1.5331535590889851</v>
@@ -6950,7 +7052,7 @@
         <v>103.4920169</v>
       </c>
       <c r="F164" t="s">
-        <v>1022</v>
+        <v>1045</v>
       </c>
       <c r="G164">
         <v>1.3573617969708751</v>
@@ -6970,7 +7072,7 @@
         <v>101.50407659999998</v>
       </c>
       <c r="F165" t="s">
-        <v>1023</v>
+        <v>1046</v>
       </c>
       <c r="G165">
         <v>3.029735493294289</v>
@@ -6990,7 +7092,7 @@
         <v>113.33650449999996</v>
       </c>
       <c r="F166" t="s">
-        <v>1024</v>
+        <v>1047</v>
       </c>
       <c r="G166">
         <v>3.555586792160975</v>
@@ -7010,7 +7112,7 @@
         <v>115.75847439999994</v>
       </c>
       <c r="F167" t="s">
-        <v>1025</v>
+        <v>1048</v>
       </c>
       <c r="G167">
         <v>5.2785055885596623</v>
@@ -7030,7 +7132,7 @@
         <v>101.66617724999406</v>
       </c>
       <c r="F168" t="s">
-        <v>1026</v>
+        <v>1049</v>
       </c>
       <c r="G168">
         <v>3.0770447932332621</v>
@@ -7050,7 +7152,7 @@
         <v>101.59598140000004</v>
       </c>
       <c r="F169" t="s">
-        <v>1027</v>
+        <v>1050</v>
       </c>
       <c r="G169">
         <v>3.3099583926885296</v>
@@ -7070,7 +7172,7 @@
         <v>101.45923422600448</v>
       </c>
       <c r="F170" t="s">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="G170">
         <v>3.0677352175300032</v>
@@ -7090,7 +7192,7 @@
         <v>101.59973779999996</v>
       </c>
       <c r="F171" t="s">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="G171">
         <v>2.9720115934194538</v>
@@ -7110,7 +7212,7 @@
         <v>101.26715</v>
       </c>
       <c r="F172" t="s">
-        <v>1030</v>
+        <v>1053</v>
       </c>
       <c r="G172">
         <v>3.3203133926663289</v>
@@ -7130,7 +7232,7 @@
         <v>102.02871229999994</v>
       </c>
       <c r="F173" t="s">
-        <v>1031</v>
+        <v>1054</v>
       </c>
       <c r="G173">
         <v>2.7324652939406082</v>
@@ -7150,7 +7252,7 @@
         <v>103.88321528994884</v>
       </c>
       <c r="F174" t="s">
-        <v>1032</v>
+        <v>1055</v>
       </c>
       <c r="G174">
         <v>1.4501504556881857</v>
@@ -7170,7 +7272,7 @@
         <v>102.91053949941212</v>
       </c>
       <c r="F175" t="s">
-        <v>1033</v>
+        <v>1056</v>
       </c>
       <c r="G175">
         <v>5.0255775904440165</v>
@@ -7190,7 +7292,7 @@
         <v>101.3295329</v>
       </c>
       <c r="F176" t="s">
-        <v>1034</v>
+        <v>1057</v>
       </c>
       <c r="G176">
         <v>5.5387327880335642</v>
@@ -7210,7 +7312,7 @@
         <v>101.74114654975544</v>
       </c>
       <c r="F177" t="s">
-        <v>1035</v>
+        <v>1058</v>
       </c>
       <c r="G177">
         <v>3.1704836931420286</v>
@@ -7230,7 +7332,7 @@
         <v>101.59700789999998</v>
       </c>
       <c r="F178" t="s">
-        <v>1036</v>
+        <v>1059</v>
       </c>
       <c r="G178">
         <v>2.8036694937853932</v>
@@ -7250,7 +7352,7 @@
         <v>109.49610289999995</v>
       </c>
       <c r="F179" t="s">
-        <v>1037</v>
+        <v>1060</v>
       </c>
       <c r="G179">
         <v>0.90651659797471162</v>
@@ -7270,7 +7372,7 @@
         <v>101.62556420000004</v>
       </c>
       <c r="F180" t="s">
-        <v>1038</v>
+        <v>1061</v>
       </c>
       <c r="G180">
         <v>3.2952497927202891</v>
@@ -7290,7 +7392,7 @@
         <v>103.62000119999998</v>
       </c>
       <c r="F181" t="s">
-        <v>1039</v>
+        <v>1062</v>
       </c>
       <c r="G181">
         <v>1.3957679968856038</v>
@@ -7310,7 +7412,7 @@
         <v>115.70921839999995</v>
       </c>
       <c r="F182" t="s">
-        <v>1040</v>
+        <v>1063</v>
       </c>
       <c r="G182">
         <v>5.2050022887092258</v>
@@ -7324,19 +7426,19 @@
         <v>609</v>
       </c>
       <c r="C183">
-        <v>5.547762874464512</v>
+        <v>3.903599722637682</v>
       </c>
       <c r="D183">
-        <v>118.42254551289872</v>
+        <v>100.88827749634127</v>
       </c>
       <c r="F183" t="s">
-        <v>1041</v>
+        <v>1064</v>
       </c>
       <c r="G183">
-        <v>5.547762874464512</v>
+        <v>3.903599722637682</v>
       </c>
       <c r="H183">
-        <v>118.42254551289872</v>
+        <v>100.88827749634127</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -7344,19 +7446,19 @@
         <v>610</v>
       </c>
       <c r="C184">
-        <v>4.8821426250816868</v>
+        <v>6.3747352133002586</v>
       </c>
       <c r="D184">
-        <v>118.08908698145486</v>
+        <v>100.53602683596614</v>
       </c>
       <c r="F184" t="s">
-        <v>1042</v>
+        <v>1065</v>
       </c>
       <c r="G184">
-        <v>4.8821426250816868</v>
+        <v>6.3747352133002586</v>
       </c>
       <c r="H184">
-        <v>118.08908698145486</v>
+        <v>100.53602683596614</v>
       </c>
     </row>
     <row r="185" spans="2:8">
@@ -7364,19 +7466,19 @@
         <v>611</v>
       </c>
       <c r="C185">
-        <v>6.6765273800166574</v>
+        <v>4.9823323832521726</v>
       </c>
       <c r="D185">
-        <v>117.20599352992348</v>
+        <v>100.74089650878858</v>
       </c>
       <c r="F185" t="s">
-        <v>1043</v>
+        <v>1066</v>
       </c>
       <c r="G185">
-        <v>6.6765273800166574</v>
+        <v>4.9823323832521726</v>
       </c>
       <c r="H185">
-        <v>117.20599352992348</v>
+        <v>100.74089650878858</v>
       </c>
     </row>
     <row r="186" spans="2:8">
@@ -7384,19 +7486,19 @@
         <v>612</v>
       </c>
       <c r="C186">
-        <v>4.5399576847101306</v>
+        <v>1.4714136640393252</v>
       </c>
       <c r="D186">
-        <v>116.96508136694317</v>
+        <v>110.37315649908444</v>
       </c>
       <c r="F186" t="s">
-        <v>1044</v>
+        <v>1067</v>
       </c>
       <c r="G186">
-        <v>4.5399576847101306</v>
+        <v>1.4714136640393252</v>
       </c>
       <c r="H186">
-        <v>116.96508136694317</v>
+        <v>110.37315649908444</v>
       </c>
     </row>
     <row r="187" spans="2:8">
@@ -7404,19 +7506,19 @@
         <v>613</v>
       </c>
       <c r="C187">
-        <v>5.6955746791523527</v>
+        <v>1.5934171680733928</v>
       </c>
       <c r="D187">
-        <v>117.4116558821934</v>
+        <v>111.89466270352284</v>
       </c>
       <c r="F187" t="s">
-        <v>1045</v>
+        <v>1068</v>
       </c>
       <c r="G187">
-        <v>5.6955746791523527</v>
+        <v>1.5934171680733928</v>
       </c>
       <c r="H187">
-        <v>117.4116558821934</v>
+        <v>111.89466270352284</v>
       </c>
     </row>
     <row r="188" spans="2:8">
@@ -7424,19 +7526,19 @@
         <v>614</v>
       </c>
       <c r="C188">
-        <v>2.7277291620423312</v>
+        <v>2.4708926440570185</v>
       </c>
       <c r="D188">
-        <v>112.67717091977651</v>
+        <v>111.91760880517153</v>
       </c>
       <c r="F188" t="s">
-        <v>1046</v>
+        <v>1069</v>
       </c>
       <c r="G188">
-        <v>2.7277291620423312</v>
+        <v>2.4708926440570185</v>
       </c>
       <c r="H188">
-        <v>112.67717091977651</v>
+        <v>111.91760880517153</v>
       </c>
     </row>
     <row r="189" spans="2:8">
@@ -7444,19 +7546,19 @@
         <v>615</v>
       </c>
       <c r="C189">
-        <v>1.4856342522550865</v>
+        <v>5.3929988172521224</v>
       </c>
       <c r="D189">
-        <v>109.92091889162116</v>
+        <v>115.92947186523736</v>
       </c>
       <c r="F189" t="s">
-        <v>1047</v>
+        <v>1070</v>
       </c>
       <c r="G189">
-        <v>1.4856342522550865</v>
+        <v>5.3929988172521224</v>
       </c>
       <c r="H189">
-        <v>109.92091889162116</v>
+        <v>115.92947186523736</v>
       </c>
     </row>
     <row r="190" spans="2:8">
@@ -7464,19 +7566,19 @@
         <v>616</v>
       </c>
       <c r="C190">
-        <v>2.560620746663369</v>
+        <v>4.3423300909311342</v>
       </c>
       <c r="D190">
-        <v>111.6254178704754</v>
+        <v>114.85202755548312</v>
       </c>
       <c r="F190" t="s">
-        <v>1048</v>
+        <v>1071</v>
       </c>
       <c r="G190">
-        <v>2.560620746663369</v>
+        <v>4.3423300909311342</v>
       </c>
       <c r="H190">
-        <v>111.6254178704754</v>
+        <v>114.85202755548312</v>
       </c>
     </row>
     <row r="191" spans="2:8">
@@ -7484,19 +7586,19 @@
         <v>617</v>
       </c>
       <c r="C191">
-        <v>1.955934998577036</v>
+        <v>1.987558726247288</v>
       </c>
       <c r="D191">
-        <v>111.98460303613192</v>
+        <v>113.18654118908776</v>
       </c>
       <c r="F191" t="s">
-        <v>1049</v>
+        <v>1072</v>
       </c>
       <c r="G191">
-        <v>1.955934998577036</v>
+        <v>1.987558726247288</v>
       </c>
       <c r="H191">
-        <v>111.98460303613192</v>
+        <v>113.18654118908776</v>
       </c>
     </row>
     <row r="192" spans="2:8">
@@ -7504,19 +7606,19 @@
         <v>618</v>
       </c>
       <c r="C192">
-        <v>1.4294404228096371</v>
+        <v>2.0159592247393485</v>
       </c>
       <c r="D192">
-        <v>111.28025650916663</v>
+        <v>114.56209043960202</v>
       </c>
       <c r="F192" t="s">
-        <v>1050</v>
+        <v>1073</v>
       </c>
       <c r="G192">
-        <v>1.4294404228096371</v>
+        <v>2.0159592247393485</v>
       </c>
       <c r="H192">
-        <v>111.28025650916663</v>
+        <v>114.56209043960202</v>
       </c>
     </row>
     <row r="193" spans="2:8">
@@ -7524,19 +7626,19 @@
         <v>619</v>
       </c>
       <c r="C193">
-        <v>5.3929988172521224</v>
+        <v>3.066168623552961</v>
       </c>
       <c r="D193">
-        <v>115.92947186523736</v>
+        <v>114.70408003592112</v>
       </c>
       <c r="F193" t="s">
-        <v>1051</v>
+        <v>1074</v>
       </c>
       <c r="G193">
-        <v>5.3929988172521224</v>
+        <v>3.066168623552961</v>
       </c>
       <c r="H193">
-        <v>115.92947186523736</v>
+        <v>114.70408003592112</v>
       </c>
     </row>
     <row r="194" spans="2:8">
@@ -7544,19 +7646,19 @@
         <v>620</v>
       </c>
       <c r="C194">
-        <v>4.457752239514889</v>
+        <v>3.7275838458134727</v>
       </c>
       <c r="D194">
-        <v>114.98825008904976</v>
+        <v>113.78253840434689</v>
       </c>
       <c r="F194" t="s">
-        <v>1052</v>
+        <v>1075</v>
       </c>
       <c r="G194">
-        <v>4.457752239514889</v>
+        <v>3.7275838458134727</v>
       </c>
       <c r="H194">
-        <v>114.98825008904976</v>
+        <v>113.78253840434689</v>
       </c>
     </row>
     <row r="195" spans="2:8">
@@ -7564,19 +7666,19 @@
         <v>621</v>
       </c>
       <c r="C195">
-        <v>1.987558726247288</v>
+        <v>2.8569578137579619</v>
       </c>
       <c r="D195">
-        <v>113.18654118908776</v>
+        <v>113.29770069642969</v>
       </c>
       <c r="F195" t="s">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="G195">
-        <v>1.987558726247288</v>
+        <v>2.8569578137579619</v>
       </c>
       <c r="H195">
-        <v>113.18654118908776</v>
+        <v>113.29770069642969</v>
       </c>
     </row>
     <row r="196" spans="2:8">
@@ -7584,19 +7686,19 @@
         <v>622</v>
       </c>
       <c r="C196">
-        <v>1.9167520366919524</v>
+        <v>5.0442125492681757</v>
       </c>
       <c r="D196">
-        <v>114.59212602002314</v>
+        <v>118.27060584793816</v>
       </c>
       <c r="F196" t="s">
-        <v>1054</v>
+        <v>1077</v>
       </c>
       <c r="G196">
-        <v>1.9167520366919524</v>
+        <v>5.0442125492681757</v>
       </c>
       <c r="H196">
-        <v>114.59212602002314</v>
+        <v>118.27060584793816</v>
       </c>
     </row>
     <row r="197" spans="2:8">
@@ -7604,19 +7706,19 @@
         <v>623</v>
       </c>
       <c r="C197">
-        <v>3.8881004411139028</v>
+        <v>4.914018649204924</v>
       </c>
       <c r="D197">
-        <v>114.03289880758678</v>
+        <v>116.97561825110354</v>
       </c>
       <c r="F197" t="s">
-        <v>1055</v>
+        <v>1078</v>
       </c>
       <c r="G197">
-        <v>3.8881004411139028</v>
+        <v>4.914018649204924</v>
       </c>
       <c r="H197">
-        <v>114.03289880758678</v>
+        <v>116.97561825110354</v>
       </c>
     </row>
     <row r="198" spans="2:8">
@@ -7624,19 +7726,19 @@
         <v>624</v>
       </c>
       <c r="C198">
-        <v>2.9933495453443268</v>
+        <v>5.9422810654848579</v>
       </c>
       <c r="D198">
-        <v>115.30173818510671</v>
+        <v>117.53144510960482</v>
       </c>
       <c r="F198" t="s">
-        <v>1056</v>
+        <v>1079</v>
       </c>
       <c r="G198">
-        <v>2.9933495453443268</v>
+        <v>5.9422810654848579</v>
       </c>
       <c r="H198">
-        <v>115.30173818510671</v>
+        <v>117.53144510960482</v>
       </c>
     </row>
     <row r="199" spans="2:8">
@@ -7644,19 +7746,19 @@
         <v>625</v>
       </c>
       <c r="C199">
-        <v>3.0281987851776679</v>
+        <v>3.360340780631597</v>
       </c>
       <c r="D199">
-        <v>113.81647739441276</v>
+        <v>103.17395441196598</v>
       </c>
       <c r="F199" t="s">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="G199">
-        <v>3.0281987851776679</v>
+        <v>3.360340780631597</v>
       </c>
       <c r="H199">
-        <v>113.81647739441276</v>
+        <v>103.17395441196598</v>
       </c>
     </row>
     <row r="200" spans="2:8">
@@ -7664,19 +7766,19 @@
         <v>626</v>
       </c>
       <c r="C200">
-        <v>6.140970818380211</v>
+        <v>1.6014295054823948</v>
       </c>
       <c r="D200">
-        <v>115.7514488147303</v>
+        <v>103.88313348657252</v>
       </c>
       <c r="F200" t="s">
-        <v>1058</v>
+        <v>1081</v>
       </c>
       <c r="G200">
-        <v>6.140970818380211</v>
+        <v>1.6014295054823948</v>
       </c>
       <c r="H200">
-        <v>115.7514488147303</v>
+        <v>103.88313348657252</v>
       </c>
     </row>
     <row r="201" spans="2:8">
@@ -7684,19 +7786,19 @@
         <v>627</v>
       </c>
       <c r="C201">
-        <v>6.5906310002424791</v>
+        <v>2.270287240919898</v>
       </c>
       <c r="D201">
-        <v>116.20115944435388</v>
+        <v>103.01043115337008</v>
       </c>
       <c r="F201" t="s">
-        <v>1059</v>
+        <v>1082</v>
       </c>
       <c r="G201">
-        <v>6.5906310002424791</v>
+        <v>2.270287240919898</v>
       </c>
       <c r="H201">
-        <v>116.20115944435388</v>
+        <v>103.01043115337008</v>
       </c>
     </row>
     <row r="202" spans="2:8">
@@ -7704,19 +7806,19 @@
         <v>628</v>
       </c>
       <c r="C202">
-        <v>6.5906310002424791</v>
+        <v>3.1095439076985012</v>
       </c>
       <c r="D202">
-        <v>116.6508700739775</v>
+        <v>102.24100044110504</v>
       </c>
       <c r="F202" t="s">
-        <v>1060</v>
+        <v>1083</v>
       </c>
       <c r="G202">
-        <v>6.5906310002424791</v>
+        <v>3.1095439076985012</v>
       </c>
       <c r="H202">
-        <v>116.6508700739775</v>
+        <v>102.24100044110504</v>
       </c>
     </row>
     <row r="203" spans="2:8">
@@ -7724,19 +7826,19 @@
         <v>629</v>
       </c>
       <c r="C203">
-        <v>7.0402911821047471</v>
+        <v>4.2434882865798587</v>
       </c>
       <c r="D203">
-        <v>116.6508700739775</v>
+        <v>102.40288390388318</v>
       </c>
       <c r="F203" t="s">
-        <v>1061</v>
+        <v>1084</v>
       </c>
       <c r="G203">
-        <v>7.0402911821047471</v>
+        <v>4.2434882865798587</v>
       </c>
       <c r="H203">
-        <v>116.6508700739775</v>
+        <v>102.40288390388318</v>
       </c>
     </row>
     <row r="204" spans="2:8">
@@ -7744,19 +7846,19 @@
         <v>630</v>
       </c>
       <c r="C204">
-        <v>7.0402911821047462</v>
+        <v>3.8982498720529488</v>
       </c>
       <c r="D204">
-        <v>117.10058070360108</v>
+        <v>101.54222976630309</v>
       </c>
       <c r="F204" t="s">
-        <v>1062</v>
+        <v>1085</v>
       </c>
       <c r="G204">
-        <v>7.0402911821047462</v>
+        <v>3.8982498720529488</v>
       </c>
       <c r="H204">
-        <v>117.10058070360108</v>
+        <v>101.54222976630309</v>
       </c>
     </row>
     <row r="205" spans="2:8">
@@ -7764,19 +7866,19 @@
         <v>631</v>
       </c>
       <c r="C205">
-        <v>7.0402911821047462</v>
+        <v>5.6293440820946481</v>
       </c>
       <c r="D205">
-        <v>117.55029133322468</v>
+        <v>101.65499175179518</v>
       </c>
       <c r="F205" t="s">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="G205">
-        <v>7.0402911821047462</v>
+        <v>5.6293440820946481</v>
       </c>
       <c r="H205">
-        <v>117.55029133322468</v>
+        <v>101.65499175179518</v>
       </c>
     </row>
     <row r="206" spans="2:8">
@@ -7784,19 +7886,19 @@
         <v>632</v>
       </c>
       <c r="C206">
-        <v>5.6045076184039964</v>
+        <v>5.4075749382724068</v>
       </c>
       <c r="D206">
-        <v>109.65914754285868</v>
+        <v>102.59025773968644</v>
       </c>
       <c r="F206" t="s">
-        <v>1064</v>
+        <v>1087</v>
       </c>
       <c r="G206">
-        <v>5.6045076184039964</v>
+        <v>5.4075749382724068</v>
       </c>
       <c r="H206">
-        <v>109.65914754285868</v>
+        <v>102.59025773968644</v>
       </c>
     </row>
     <row r="207" spans="2:8">
@@ -7804,19 +7906,19 @@
         <v>633</v>
       </c>
       <c r="C207">
-        <v>6.046176460479697</v>
+        <v>7.0402911821047454</v>
       </c>
       <c r="D207">
-        <v>105.162469611776</v>
+        <v>117.105668862972</v>
       </c>
       <c r="F207" t="s">
-        <v>1065</v>
+        <v>1088</v>
       </c>
       <c r="G207">
-        <v>6.046176460479697</v>
+        <v>7.0402911821047454</v>
       </c>
       <c r="H207">
-        <v>105.162469611776</v>
+        <v>117.105668862972</v>
       </c>
     </row>
     <row r="208" spans="2:8">
@@ -7824,19 +7926,19 @@
         <v>634</v>
       </c>
       <c r="C208">
-        <v>6.7461745147771301</v>
+        <v>6.5649053418561509</v>
       </c>
       <c r="D208">
-        <v>104.85327537436562</v>
+        <v>116.17543089978388</v>
       </c>
       <c r="F208" t="s">
-        <v>1066</v>
+        <v>1089</v>
       </c>
       <c r="G208">
-        <v>6.7461745147771301</v>
+        <v>6.5649053418561509</v>
       </c>
       <c r="H208">
-        <v>104.85327537436562</v>
+        <v>116.17543089978388</v>
       </c>
     </row>
     <row r="209" spans="2:8">
@@ -7844,19 +7946,19 @@
         <v>635</v>
       </c>
       <c r="C209">
-        <v>6.9459261254604954</v>
+        <v>6.7125380812178737</v>
       </c>
       <c r="D209">
-        <v>115.7814452601516</v>
+        <v>116.6508700739775</v>
       </c>
       <c r="F209" t="s">
-        <v>1067</v>
+        <v>1090</v>
       </c>
       <c r="G209">
-        <v>6.9459261254604954</v>
+        <v>6.7125380812178737</v>
       </c>
       <c r="H209">
-        <v>115.7814452601516</v>
+        <v>116.6508700739775</v>
       </c>
     </row>
     <row r="210" spans="2:8">
@@ -7864,19 +7966,19 @@
         <v>636</v>
       </c>
       <c r="C210">
-        <v>7.5006050281671213</v>
+        <v>1.6379439693624995</v>
       </c>
       <c r="D210">
-        <v>116.40480846375353</v>
+        <v>104.16008099381914</v>
       </c>
       <c r="F210" t="s">
-        <v>1068</v>
+        <v>1091</v>
       </c>
       <c r="G210">
-        <v>7.5006050281671213</v>
+        <v>1.6379439693624995</v>
       </c>
       <c r="H210">
-        <v>116.40480846375353</v>
+        <v>104.16008099381914</v>
       </c>
     </row>
     <row r="211" spans="2:8">
@@ -7884,19 +7986,19 @@
         <v>637</v>
       </c>
       <c r="C211">
-        <v>7.4058634641483678</v>
+        <v>1.1947088178952514</v>
       </c>
       <c r="D211">
-        <v>115.94469379525212</v>
+        <v>103.9914448614589</v>
       </c>
       <c r="F211" t="s">
-        <v>1069</v>
+        <v>1092</v>
       </c>
       <c r="G211">
-        <v>7.4058634641483678</v>
+        <v>1.1947088178952514</v>
       </c>
       <c r="H211">
-        <v>115.94469379525212</v>
+        <v>103.9914448614589</v>
       </c>
     </row>
     <row r="212" spans="2:8">
@@ -7904,19 +8006,19 @@
         <v>638</v>
       </c>
       <c r="C212">
-        <v>6.6045941307841005</v>
+        <v>6.140970818380211</v>
       </c>
       <c r="D212">
-        <v>112.94318422934199</v>
+        <v>100.01157677790444</v>
       </c>
       <c r="F212" t="s">
-        <v>1070</v>
+        <v>1093</v>
       </c>
       <c r="G212">
-        <v>6.6045941307841005</v>
+        <v>6.140970818380211</v>
       </c>
       <c r="H212">
-        <v>112.94318422934199</v>
+        <v>100.01157677790444</v>
       </c>
     </row>
     <row r="213" spans="2:8">
@@ -7924,19 +8026,19 @@
         <v>639</v>
       </c>
       <c r="C213">
-        <v>8.5734175815983793</v>
+        <v>6.5906310002424782</v>
       </c>
       <c r="D213">
-        <v>113.8254901603638</v>
+        <v>100.01157677790444</v>
       </c>
       <c r="F213" t="s">
-        <v>1071</v>
+        <v>1094</v>
       </c>
       <c r="G213">
-        <v>8.5734175815983793</v>
+        <v>6.5906310002424782</v>
       </c>
       <c r="H213">
-        <v>113.8254901603638</v>
+        <v>100.01157677790444</v>
       </c>
     </row>
     <row r="214" spans="2:8">
@@ -7944,19 +8046,19 @@
         <v>640</v>
       </c>
       <c r="C214">
-        <v>8.4950609361706633</v>
+        <v>4.407329846042912</v>
       </c>
       <c r="D214">
-        <v>114.71244133364924</v>
+        <v>103.60926181489326</v>
       </c>
       <c r="F214" t="s">
-        <v>1072</v>
+        <v>1095</v>
       </c>
       <c r="G214">
-        <v>8.4950609361706633</v>
+        <v>4.407329846042912</v>
       </c>
       <c r="H214">
-        <v>114.71244133364924</v>
+        <v>103.60926181489326</v>
       </c>
     </row>
     <row r="215" spans="2:8">
@@ -7964,18 +8066,238 @@
         <v>641</v>
       </c>
       <c r="C215">
+        <v>2.6015909698094069</v>
+      </c>
+      <c r="D215">
+        <v>104.15145447410208</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G215">
+        <v>2.6015909698094069</v>
+      </c>
+      <c r="H215">
+        <v>104.15145447410208</v>
+      </c>
+    </row>
+    <row r="216" spans="2:8">
+      <c r="B216" t="s">
+        <v>642</v>
+      </c>
+      <c r="C216">
+        <v>3.2777874571098491</v>
+      </c>
+      <c r="D216">
+        <v>103.60926181489324</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G216">
+        <v>3.2777874571098491</v>
+      </c>
+      <c r="H216">
+        <v>103.60926181489324</v>
+      </c>
+    </row>
+    <row r="217" spans="2:8">
+      <c r="B217" t="s">
+        <v>643</v>
+      </c>
+      <c r="C217">
+        <v>5.6045076184039964</v>
+      </c>
+      <c r="D217">
+        <v>109.65914754285868</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G217">
+        <v>5.6045076184039964</v>
+      </c>
+      <c r="H217">
+        <v>109.65914754285868</v>
+      </c>
+    </row>
+    <row r="218" spans="2:8">
+      <c r="B218" t="s">
+        <v>644</v>
+      </c>
+      <c r="C218">
+        <v>6.046176460479697</v>
+      </c>
+      <c r="D218">
+        <v>105.162469611776</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G218">
+        <v>6.046176460479697</v>
+      </c>
+      <c r="H218">
+        <v>105.162469611776</v>
+      </c>
+    </row>
+    <row r="219" spans="2:8">
+      <c r="B219" t="s">
+        <v>645</v>
+      </c>
+      <c r="C219">
+        <v>6.7461745147771301</v>
+      </c>
+      <c r="D219">
+        <v>104.85327537436562</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G219">
+        <v>6.7461745147771301</v>
+      </c>
+      <c r="H219">
+        <v>104.85327537436562</v>
+      </c>
+    </row>
+    <row r="220" spans="2:8">
+      <c r="B220" t="s">
+        <v>646</v>
+      </c>
+      <c r="C220">
+        <v>6.9459261254604954</v>
+      </c>
+      <c r="D220">
+        <v>115.7814452601516</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G220">
+        <v>6.9459261254604954</v>
+      </c>
+      <c r="H220">
+        <v>115.7814452601516</v>
+      </c>
+    </row>
+    <row r="221" spans="2:8">
+      <c r="B221" t="s">
+        <v>647</v>
+      </c>
+      <c r="C221">
+        <v>7.5006050281671213</v>
+      </c>
+      <c r="D221">
+        <v>116.40480846375353</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G221">
+        <v>7.5006050281671213</v>
+      </c>
+      <c r="H221">
+        <v>116.40480846375353</v>
+      </c>
+    </row>
+    <row r="222" spans="2:8">
+      <c r="B222" t="s">
+        <v>648</v>
+      </c>
+      <c r="C222">
+        <v>7.4058634641483678</v>
+      </c>
+      <c r="D222">
+        <v>115.94469379525212</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G222">
+        <v>7.4058634641483678</v>
+      </c>
+      <c r="H222">
+        <v>115.94469379525212</v>
+      </c>
+    </row>
+    <row r="223" spans="2:8">
+      <c r="B223" t="s">
+        <v>649</v>
+      </c>
+      <c r="C223">
+        <v>6.6045941307841005</v>
+      </c>
+      <c r="D223">
+        <v>112.94318422934199</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G223">
+        <v>6.6045941307841005</v>
+      </c>
+      <c r="H223">
+        <v>112.94318422934199</v>
+      </c>
+    </row>
+    <row r="224" spans="2:8">
+      <c r="B224" t="s">
+        <v>650</v>
+      </c>
+      <c r="C224">
+        <v>8.5734175815983793</v>
+      </c>
+      <c r="D224">
+        <v>113.8254901603638</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G224">
+        <v>8.5734175815983793</v>
+      </c>
+      <c r="H224">
+        <v>113.8254901603638</v>
+      </c>
+    </row>
+    <row r="225" spans="2:8">
+      <c r="B225" t="s">
+        <v>651</v>
+      </c>
+      <c r="C225">
+        <v>8.4950609361706633</v>
+      </c>
+      <c r="D225">
+        <v>114.71244133364924</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G225">
+        <v>8.4950609361706633</v>
+      </c>
+      <c r="H225">
+        <v>114.71244133364924</v>
+      </c>
+    </row>
+    <row r="226" spans="2:8">
+      <c r="B226" t="s">
+        <v>652</v>
+      </c>
+      <c r="C226">
         <v>7.7335093286347485</v>
       </c>
-      <c r="D215">
+      <c r="D226">
         <v>114.1424214358937</v>
       </c>
-      <c r="F215" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G215">
+      <c r="F226" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G226">
         <v>7.7335093286347485</v>
       </c>
-      <c r="H215">
+      <c r="H226">
         <v>114.1424214358937</v>
       </c>
     </row>
@@ -24098,8 +24420,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E0A671-08FB-443A-86CF-4137A0B2CDFB}">
-  <dimension ref="B9:L215"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C2A52F-55E7-4F13-B58D-02EC98A85C10}">
+  <dimension ref="B9:L226"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:12">
@@ -24156,19 +24478,19 @@
         <v>437</v>
       </c>
       <c r="G11" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H11" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="J11" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K11" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="L11" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -24185,19 +24507,19 @@
         <v>438</v>
       </c>
       <c r="G12" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H12" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J12" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K12" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="L12" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -24214,19 +24536,19 @@
         <v>439</v>
       </c>
       <c r="G13" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H13" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J13" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K13" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="L13" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -24243,19 +24565,19 @@
         <v>440</v>
       </c>
       <c r="G14" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H14" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J14" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K14" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="L14" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -24272,19 +24594,19 @@
         <v>441</v>
       </c>
       <c r="G15" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H15" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J15" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K15" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="L15" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -24301,19 +24623,19 @@
         <v>442</v>
       </c>
       <c r="G16" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H16" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J16" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K16" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="L16" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -24330,19 +24652,19 @@
         <v>443</v>
       </c>
       <c r="G17" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H17" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J17" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K17" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="L17" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -24359,19 +24681,19 @@
         <v>444</v>
       </c>
       <c r="G18" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H18" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J18" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K18" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="L18" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -24388,19 +24710,19 @@
         <v>445</v>
       </c>
       <c r="G19" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H19" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J19" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K19" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="L19" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -24417,19 +24739,19 @@
         <v>446</v>
       </c>
       <c r="G20" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H20" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J20" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K20" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="L20" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -24446,19 +24768,19 @@
         <v>447</v>
       </c>
       <c r="G21" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H21" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J21" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K21" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="L21" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -24475,19 +24797,19 @@
         <v>448</v>
       </c>
       <c r="G22" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H22" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="J22" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K22" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="L22" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -24504,19 +24826,19 @@
         <v>449</v>
       </c>
       <c r="G23" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H23" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="J23" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="L23" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -24533,19 +24855,19 @@
         <v>450</v>
       </c>
       <c r="G24" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H24" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J24" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K24" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="L24" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -24562,19 +24884,19 @@
         <v>451</v>
       </c>
       <c r="G25" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H25" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="J25" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="L25" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -24591,19 +24913,19 @@
         <v>452</v>
       </c>
       <c r="G26" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H26" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J26" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="L26" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -24620,19 +24942,19 @@
         <v>453</v>
       </c>
       <c r="G27" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H27" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J27" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K27" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="L27" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -24649,19 +24971,19 @@
         <v>454</v>
       </c>
       <c r="G28" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H28" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J28" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K28" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="L28" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -24678,19 +25000,19 @@
         <v>455</v>
       </c>
       <c r="G29" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H29" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J29" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K29" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="L29" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -24707,19 +25029,19 @@
         <v>456</v>
       </c>
       <c r="G30" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H30" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J30" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K30" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="L30" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -24736,19 +25058,19 @@
         <v>457</v>
       </c>
       <c r="G31" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H31" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J31" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K31" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="L31" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -24765,19 +25087,19 @@
         <v>458</v>
       </c>
       <c r="G32" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H32" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J32" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K32" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="L32" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -24794,19 +25116,19 @@
         <v>459</v>
       </c>
       <c r="G33" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H33" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J33" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K33" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="L33" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -24823,19 +25145,19 @@
         <v>460</v>
       </c>
       <c r="G34" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H34" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J34" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K34" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="L34" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -24852,19 +25174,19 @@
         <v>461</v>
       </c>
       <c r="G35" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H35" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="J35" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K35" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="L35" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -24881,19 +25203,19 @@
         <v>462</v>
       </c>
       <c r="G36" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H36" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J36" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K36" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="L36" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -24910,19 +25232,19 @@
         <v>463</v>
       </c>
       <c r="G37" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H37" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J37" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K37" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="L37" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -24939,19 +25261,19 @@
         <v>464</v>
       </c>
       <c r="G38" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H38" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J38" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K38" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="L38" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -24968,19 +25290,19 @@
         <v>465</v>
       </c>
       <c r="G39" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H39" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J39" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K39" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="L39" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -24997,19 +25319,19 @@
         <v>466</v>
       </c>
       <c r="G40" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H40" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J40" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K40" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="L40" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -25026,19 +25348,19 @@
         <v>467</v>
       </c>
       <c r="G41" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H41" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J41" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K41" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="L41" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -25055,19 +25377,19 @@
         <v>468</v>
       </c>
       <c r="G42" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H42" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J42" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K42" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="L42" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -25084,19 +25406,19 @@
         <v>469</v>
       </c>
       <c r="G43" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H43" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J43" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K43" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="L43" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -25113,19 +25435,19 @@
         <v>470</v>
       </c>
       <c r="G44" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H44" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J44" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K44" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="L44" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -25142,19 +25464,19 @@
         <v>471</v>
       </c>
       <c r="G45" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H45" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J45" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K45" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="L45" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -25171,19 +25493,19 @@
         <v>472</v>
       </c>
       <c r="G46" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H46" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J46" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K46" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="L46" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -25200,19 +25522,19 @@
         <v>473</v>
       </c>
       <c r="G47" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H47" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J47" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K47" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="L47" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -25229,19 +25551,19 @@
         <v>474</v>
       </c>
       <c r="G48" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H48" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J48" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K48" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="L48" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -25258,19 +25580,19 @@
         <v>475</v>
       </c>
       <c r="G49" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H49" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J49" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K49" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="L49" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -25287,19 +25609,19 @@
         <v>476</v>
       </c>
       <c r="G50" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H50" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J50" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K50" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="L50" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -25316,19 +25638,19 @@
         <v>477</v>
       </c>
       <c r="G51" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H51" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J51" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K51" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="L51" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -25345,19 +25667,19 @@
         <v>478</v>
       </c>
       <c r="G52" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H52" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J52" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K52" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="L52" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -25374,19 +25696,19 @@
         <v>479</v>
       </c>
       <c r="G53" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H53" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J53" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K53" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="L53" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -25403,19 +25725,19 @@
         <v>480</v>
       </c>
       <c r="G54" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H54" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J54" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K54" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="L54" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -25432,19 +25754,19 @@
         <v>481</v>
       </c>
       <c r="G55" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H55" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J55" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K55" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="L55" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -25461,19 +25783,19 @@
         <v>482</v>
       </c>
       <c r="G56" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H56" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J56" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K56" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="L56" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -25490,19 +25812,19 @@
         <v>483</v>
       </c>
       <c r="G57" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H57" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J57" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K57" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="L57" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -25519,19 +25841,19 @@
         <v>484</v>
       </c>
       <c r="G58" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H58" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="J58" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K58" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="L58" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -25548,19 +25870,19 @@
         <v>485</v>
       </c>
       <c r="G59" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H59" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J59" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K59" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="L59" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -25577,19 +25899,19 @@
         <v>486</v>
       </c>
       <c r="G60" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H60" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J60" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K60" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="L60" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -25606,19 +25928,19 @@
         <v>487</v>
       </c>
       <c r="G61" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H61" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J61" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K61" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="L61" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -25635,19 +25957,19 @@
         <v>488</v>
       </c>
       <c r="G62" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H62" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="J62" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K62" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="L62" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -25664,19 +25986,19 @@
         <v>489</v>
       </c>
       <c r="G63" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H63" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J63" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K63" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="L63" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -25693,19 +26015,19 @@
         <v>490</v>
       </c>
       <c r="G64" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H64" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J64" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K64" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="L64" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -25722,19 +26044,19 @@
         <v>491</v>
       </c>
       <c r="G65" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H65" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="J65" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K65" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="L65" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -25751,19 +26073,19 @@
         <v>492</v>
       </c>
       <c r="G66" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H66" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J66" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K66" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="L66" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -25780,19 +26102,19 @@
         <v>493</v>
       </c>
       <c r="G67" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H67" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J67" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K67" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="L67" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -25809,19 +26131,19 @@
         <v>494</v>
       </c>
       <c r="G68" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H68" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J68" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K68" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="L68" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -25838,19 +26160,19 @@
         <v>495</v>
       </c>
       <c r="G69" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H69" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J69" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K69" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="L69" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -25867,19 +26189,19 @@
         <v>496</v>
       </c>
       <c r="G70" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H70" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J70" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K70" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="L70" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -25896,19 +26218,19 @@
         <v>497</v>
       </c>
       <c r="G71" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H71" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J71" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K71" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="L71" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -25925,19 +26247,19 @@
         <v>498</v>
       </c>
       <c r="G72" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H72" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J72" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K72" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="L72" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -25954,19 +26276,19 @@
         <v>499</v>
       </c>
       <c r="G73" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H73" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J73" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K73" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="L73" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -25983,19 +26305,19 @@
         <v>500</v>
       </c>
       <c r="G74" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H74" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J74" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K74" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="L74" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -26012,19 +26334,19 @@
         <v>501</v>
       </c>
       <c r="G75" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H75" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J75" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K75" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="L75" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -26041,19 +26363,19 @@
         <v>502</v>
       </c>
       <c r="G76" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H76" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J76" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K76" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="L76" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -26070,19 +26392,19 @@
         <v>503</v>
       </c>
       <c r="G77" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H77" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="J77" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K77" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="L77" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -26099,19 +26421,19 @@
         <v>504</v>
       </c>
       <c r="G78" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H78" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J78" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K78" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="L78" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -26128,19 +26450,19 @@
         <v>505</v>
       </c>
       <c r="G79" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H79" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J79" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K79" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="L79" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -26157,19 +26479,19 @@
         <v>506</v>
       </c>
       <c r="G80" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H80" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J80" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K80" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="L80" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -26186,19 +26508,19 @@
         <v>507</v>
       </c>
       <c r="G81" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H81" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J81" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K81" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="L81" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -26215,19 +26537,19 @@
         <v>508</v>
       </c>
       <c r="G82" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H82" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J82" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K82" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="L82" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -26244,19 +26566,19 @@
         <v>509</v>
       </c>
       <c r="G83" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H83" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J83" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K83" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="L83" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -26273,19 +26595,19 @@
         <v>510</v>
       </c>
       <c r="G84" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H84" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J84" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K84" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="L84" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -26302,19 +26624,19 @@
         <v>511</v>
       </c>
       <c r="G85" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H85" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J85" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K85" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="L85" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -26331,19 +26653,19 @@
         <v>512</v>
       </c>
       <c r="G86" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H86" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J86" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K86" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="L86" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -26360,19 +26682,19 @@
         <v>513</v>
       </c>
       <c r="G87" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H87" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J87" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K87" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="L87" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -26389,19 +26711,19 @@
         <v>514</v>
       </c>
       <c r="G88" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H88" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J88" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K88" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="L88" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -26418,19 +26740,19 @@
         <v>515</v>
       </c>
       <c r="G89" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H89" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J89" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K89" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="L89" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -26447,19 +26769,19 @@
         <v>516</v>
       </c>
       <c r="G90" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H90" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J90" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K90" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="L90" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -26476,19 +26798,19 @@
         <v>517</v>
       </c>
       <c r="G91" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H91" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J91" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K91" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="L91" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -26505,19 +26827,19 @@
         <v>518</v>
       </c>
       <c r="G92" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H92" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J92" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K92" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="L92" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -26534,19 +26856,19 @@
         <v>519</v>
       </c>
       <c r="G93" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H93" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J93" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K93" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="L93" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -26563,19 +26885,19 @@
         <v>520</v>
       </c>
       <c r="G94" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H94" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J94" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K94" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="L94" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -26592,19 +26914,19 @@
         <v>521</v>
       </c>
       <c r="G95" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H95" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J95" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K95" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="L95" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -26621,19 +26943,19 @@
         <v>522</v>
       </c>
       <c r="G96" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H96" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J96" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K96" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="L96" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -26650,19 +26972,19 @@
         <v>523</v>
       </c>
       <c r="G97" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H97" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="J97" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K97" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="L97" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -26679,19 +27001,19 @@
         <v>524</v>
       </c>
       <c r="G98" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H98" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J98" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K98" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="L98" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -26708,19 +27030,19 @@
         <v>525</v>
       </c>
       <c r="G99" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H99" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J99" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K99" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="L99" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -26737,19 +27059,19 @@
         <v>526</v>
       </c>
       <c r="G100" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H100" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J100" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K100" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="L100" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -26766,19 +27088,19 @@
         <v>527</v>
       </c>
       <c r="G101" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H101" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J101" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K101" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="L101" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -26795,19 +27117,19 @@
         <v>528</v>
       </c>
       <c r="G102" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H102" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J102" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K102" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="L102" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -26824,19 +27146,19 @@
         <v>529</v>
       </c>
       <c r="G103" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H103" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J103" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K103" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="L103" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -26853,19 +27175,19 @@
         <v>530</v>
       </c>
       <c r="G104" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H104" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J104" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K104" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="L104" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -26882,19 +27204,19 @@
         <v>531</v>
       </c>
       <c r="G105" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H105" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J105" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K105" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="L105" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -26911,19 +27233,19 @@
         <v>532</v>
       </c>
       <c r="G106" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H106" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J106" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K106" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="L106" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -26940,19 +27262,19 @@
         <v>533</v>
       </c>
       <c r="G107" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H107" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J107" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K107" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="L107" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -26969,19 +27291,19 @@
         <v>534</v>
       </c>
       <c r="G108" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H108" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J108" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K108" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="L108" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -26998,19 +27320,19 @@
         <v>535</v>
       </c>
       <c r="G109" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H109" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J109" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K109" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="L109" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -27027,19 +27349,19 @@
         <v>536</v>
       </c>
       <c r="G110" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H110" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J110" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K110" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="L110" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -27056,19 +27378,19 @@
         <v>537</v>
       </c>
       <c r="G111" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H111" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J111" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K111" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="L111" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -27085,19 +27407,19 @@
         <v>538</v>
       </c>
       <c r="G112" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H112" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J112" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K112" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="L112" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -27114,19 +27436,19 @@
         <v>539</v>
       </c>
       <c r="G113" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H113" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J113" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K113" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="L113" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -27143,19 +27465,19 @@
         <v>540</v>
       </c>
       <c r="G114" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H114" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J114" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K114" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="L114" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -27172,19 +27494,19 @@
         <v>541</v>
       </c>
       <c r="G115" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H115" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J115" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K115" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="L115" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -27201,19 +27523,19 @@
         <v>542</v>
       </c>
       <c r="G116" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H116" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J116" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K116" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="L116" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -27230,19 +27552,19 @@
         <v>543</v>
       </c>
       <c r="G117" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H117" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J117" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K117" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="L117" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -27259,19 +27581,19 @@
         <v>544</v>
       </c>
       <c r="G118" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H118" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="J118" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K118" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="L118" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -27288,19 +27610,19 @@
         <v>545</v>
       </c>
       <c r="G119" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H119" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J119" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K119" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="L119" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -27317,19 +27639,19 @@
         <v>546</v>
       </c>
       <c r="G120" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H120" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="J120" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K120" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="L120" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -27346,19 +27668,19 @@
         <v>547</v>
       </c>
       <c r="G121" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H121" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J121" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K121" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="L121" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -27375,19 +27697,19 @@
         <v>548</v>
       </c>
       <c r="G122" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H122" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J122" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K122" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="L122" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -27404,19 +27726,19 @@
         <v>549</v>
       </c>
       <c r="G123" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H123" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J123" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K123" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="L123" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -27433,19 +27755,19 @@
         <v>550</v>
       </c>
       <c r="G124" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H124" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J124" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K124" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="L124" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -27462,19 +27784,19 @@
         <v>551</v>
       </c>
       <c r="G125" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H125" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J125" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K125" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="L125" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -27491,19 +27813,19 @@
         <v>552</v>
       </c>
       <c r="G126" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H126" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J126" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K126" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="L126" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -27520,19 +27842,19 @@
         <v>553</v>
       </c>
       <c r="G127" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H127" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J127" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K127" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="L127" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -27549,19 +27871,19 @@
         <v>554</v>
       </c>
       <c r="G128" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H128" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J128" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K128" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="L128" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -27578,19 +27900,19 @@
         <v>555</v>
       </c>
       <c r="G129" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H129" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J129" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K129" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="L129" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -27607,19 +27929,19 @@
         <v>556</v>
       </c>
       <c r="G130" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H130" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="J130" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K130" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="L130" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -27636,19 +27958,19 @@
         <v>557</v>
       </c>
       <c r="G131" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H131" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J131" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K131" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="L131" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -27665,19 +27987,19 @@
         <v>558</v>
       </c>
       <c r="G132" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H132" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="J132" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K132" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="L132" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -27694,19 +28016,19 @@
         <v>559</v>
       </c>
       <c r="G133" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H133" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="J133" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K133" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="L133" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -27723,19 +28045,19 @@
         <v>560</v>
       </c>
       <c r="G134" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H134" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J134" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K134" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="L134" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -27752,19 +28074,19 @@
         <v>561</v>
       </c>
       <c r="G135" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H135" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J135" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K135" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="L135" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -27781,19 +28103,19 @@
         <v>562</v>
       </c>
       <c r="G136" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H136" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J136" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K136" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="L136" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -27810,19 +28132,19 @@
         <v>563</v>
       </c>
       <c r="G137" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H137" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J137" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K137" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="L137" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -27839,19 +28161,19 @@
         <v>564</v>
       </c>
       <c r="G138" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H138" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J138" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K138" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="L138" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
     </row>
     <row r="139" spans="2:12">
@@ -27868,19 +28190,19 @@
         <v>565</v>
       </c>
       <c r="G139" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H139" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J139" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K139" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="L139" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
     </row>
     <row r="140" spans="2:12">
@@ -27897,19 +28219,19 @@
         <v>566</v>
       </c>
       <c r="G140" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H140" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="J140" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K140" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="L140" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
     </row>
     <row r="141" spans="2:12">
@@ -27926,19 +28248,19 @@
         <v>567</v>
       </c>
       <c r="G141" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H141" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J141" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K141" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="L141" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
     </row>
     <row r="142" spans="2:12">
@@ -27955,19 +28277,19 @@
         <v>568</v>
       </c>
       <c r="G142" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H142" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J142" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K142" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="L142" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
     </row>
     <row r="143" spans="2:12">
@@ -27984,19 +28306,19 @@
         <v>569</v>
       </c>
       <c r="G143" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H143" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J143" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K143" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="L143" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="144" spans="2:12">
@@ -28013,19 +28335,19 @@
         <v>570</v>
       </c>
       <c r="G144" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H144" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J144" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K144" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="L144" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
     </row>
     <row r="145" spans="2:12">
@@ -28042,19 +28364,19 @@
         <v>571</v>
       </c>
       <c r="G145" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H145" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J145" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K145" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="L145" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
     </row>
     <row r="146" spans="2:12">
@@ -28071,19 +28393,19 @@
         <v>572</v>
       </c>
       <c r="G146" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H146" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J146" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K146" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="L146" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
     </row>
     <row r="147" spans="2:12">
@@ -28100,19 +28422,19 @@
         <v>573</v>
       </c>
       <c r="G147" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H147" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J147" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K147" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="L147" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
     </row>
     <row r="148" spans="2:12">
@@ -28129,19 +28451,19 @@
         <v>574</v>
       </c>
       <c r="G148" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H148" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J148" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K148" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="L148" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
     </row>
     <row r="149" spans="2:12">
@@ -28158,19 +28480,19 @@
         <v>575</v>
       </c>
       <c r="G149" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H149" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J149" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K149" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="L149" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
     </row>
     <row r="150" spans="2:12">
@@ -28187,19 +28509,19 @@
         <v>576</v>
       </c>
       <c r="G150" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H150" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J150" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K150" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="L150" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
     </row>
     <row r="151" spans="2:12">
@@ -28216,19 +28538,19 @@
         <v>577</v>
       </c>
       <c r="G151" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H151" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J151" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K151" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="L151" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
     </row>
     <row r="152" spans="2:12">
@@ -28245,19 +28567,19 @@
         <v>578</v>
       </c>
       <c r="G152" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H152" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J152" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K152" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="L152" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
     </row>
     <row r="153" spans="2:12">
@@ -28274,19 +28596,19 @@
         <v>579</v>
       </c>
       <c r="G153" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H153" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J153" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K153" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="L153" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
     </row>
     <row r="154" spans="2:12">
@@ -28303,19 +28625,19 @@
         <v>580</v>
       </c>
       <c r="G154" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H154" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J154" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K154" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="L154" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
     </row>
     <row r="155" spans="2:12">
@@ -28332,19 +28654,19 @@
         <v>581</v>
       </c>
       <c r="G155" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H155" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J155" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K155" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="L155" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
     </row>
     <row r="156" spans="2:12">
@@ -28361,19 +28683,19 @@
         <v>582</v>
       </c>
       <c r="G156" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H156" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J156" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K156" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="L156" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
     </row>
     <row r="157" spans="2:12">
@@ -28390,19 +28712,19 @@
         <v>583</v>
       </c>
       <c r="G157" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H157" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J157" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K157" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="L157" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
     </row>
     <row r="158" spans="2:12">
@@ -28419,19 +28741,19 @@
         <v>584</v>
       </c>
       <c r="G158" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H158" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="J158" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K158" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="L158" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="159" spans="2:12">
@@ -28448,19 +28770,19 @@
         <v>585</v>
       </c>
       <c r="G159" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H159" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J159" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K159" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="L159" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
     </row>
     <row r="160" spans="2:12">
@@ -28477,19 +28799,19 @@
         <v>586</v>
       </c>
       <c r="G160" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H160" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J160" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K160" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="L160" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="161" spans="2:12">
@@ -28506,19 +28828,19 @@
         <v>587</v>
       </c>
       <c r="G161" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H161" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J161" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K161" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="L161" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
     </row>
     <row r="162" spans="2:12">
@@ -28535,19 +28857,19 @@
         <v>588</v>
       </c>
       <c r="G162" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H162" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J162" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K162" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="L162" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
     </row>
     <row r="163" spans="2:12">
@@ -28564,19 +28886,19 @@
         <v>589</v>
       </c>
       <c r="G163" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H163" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J163" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K163" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="L163" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
     </row>
     <row r="164" spans="2:12">
@@ -28593,19 +28915,19 @@
         <v>590</v>
       </c>
       <c r="G164" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H164" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J164" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K164" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="L164" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
     </row>
     <row r="165" spans="2:12">
@@ -28622,19 +28944,19 @@
         <v>591</v>
       </c>
       <c r="G165" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H165" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J165" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K165" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="L165" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
     </row>
     <row r="166" spans="2:12">
@@ -28651,19 +28973,19 @@
         <v>592</v>
       </c>
       <c r="G166" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H166" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J166" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K166" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="L166" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
     </row>
     <row r="167" spans="2:12">
@@ -28680,19 +29002,19 @@
         <v>593</v>
       </c>
       <c r="G167" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H167" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="J167" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K167" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="L167" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
     </row>
     <row r="168" spans="2:12">
@@ -28709,19 +29031,19 @@
         <v>594</v>
       </c>
       <c r="G168" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H168" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J168" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K168" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="L168" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
     </row>
     <row r="169" spans="2:12">
@@ -28738,19 +29060,19 @@
         <v>595</v>
       </c>
       <c r="G169" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H169" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J169" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K169" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="L169" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
     </row>
     <row r="170" spans="2:12">
@@ -28767,19 +29089,19 @@
         <v>596</v>
       </c>
       <c r="G170" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H170" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J170" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K170" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="L170" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="171" spans="2:12">
@@ -28796,19 +29118,19 @@
         <v>597</v>
       </c>
       <c r="G171" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H171" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J171" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K171" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="L171" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
     </row>
     <row r="172" spans="2:12">
@@ -28825,19 +29147,19 @@
         <v>598</v>
       </c>
       <c r="G172" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H172" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J172" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K172" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="L172" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
     </row>
     <row r="173" spans="2:12">
@@ -28854,19 +29176,19 @@
         <v>599</v>
       </c>
       <c r="G173" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H173" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="J173" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K173" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="L173" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
     </row>
     <row r="174" spans="2:12">
@@ -28883,19 +29205,19 @@
         <v>600</v>
       </c>
       <c r="G174" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H174" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J174" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K174" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="L174" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
     </row>
     <row r="175" spans="2:12">
@@ -28912,19 +29234,19 @@
         <v>601</v>
       </c>
       <c r="G175" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H175" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="J175" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K175" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="L175" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
     </row>
     <row r="176" spans="2:12">
@@ -28941,19 +29263,19 @@
         <v>602</v>
       </c>
       <c r="G176" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H176" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="J176" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K176" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="L176" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
     </row>
     <row r="177" spans="2:12">
@@ -28970,19 +29292,19 @@
         <v>603</v>
       </c>
       <c r="G177" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H177" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="J177" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K177" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="L177" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
     </row>
     <row r="178" spans="2:12">
@@ -28999,19 +29321,19 @@
         <v>604</v>
       </c>
       <c r="G178" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H178" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J178" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K178" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="L178" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
     </row>
     <row r="179" spans="2:12">
@@ -29028,19 +29350,19 @@
         <v>605</v>
       </c>
       <c r="G179" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H179" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="J179" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K179" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="L179" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
     </row>
     <row r="180" spans="2:12">
@@ -29057,19 +29379,19 @@
         <v>606</v>
       </c>
       <c r="G180" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H180" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="J180" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K180" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="L180" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
     </row>
     <row r="181" spans="2:12">
@@ -29086,19 +29408,19 @@
         <v>607</v>
       </c>
       <c r="G181" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H181" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J181" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K181" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="L181" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
     </row>
     <row r="182" spans="2:12">
@@ -29115,19 +29437,19 @@
         <v>608</v>
       </c>
       <c r="G182" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H182" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="J182" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K182" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="L182" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
     </row>
     <row r="183" spans="2:12">
@@ -29144,19 +29466,19 @@
         <v>609</v>
       </c>
       <c r="G183" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H183" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="J183" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K183" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="L183" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
     </row>
     <row r="184" spans="2:12">
@@ -29173,19 +29495,19 @@
         <v>610</v>
       </c>
       <c r="G184" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H184" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="J184" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K184" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="L184" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
     </row>
     <row r="185" spans="2:12">
@@ -29202,19 +29524,19 @@
         <v>611</v>
       </c>
       <c r="G185" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H185" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="J185" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K185" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="L185" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
     </row>
     <row r="186" spans="2:12">
@@ -29231,19 +29553,19 @@
         <v>612</v>
       </c>
       <c r="G186" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H186" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="J186" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K186" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="L186" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="187" spans="2:12">
@@ -29260,19 +29582,19 @@
         <v>613</v>
       </c>
       <c r="G187" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H187" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="J187" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K187" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="L187" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
     </row>
     <row r="188" spans="2:12">
@@ -29289,19 +29611,19 @@
         <v>614</v>
       </c>
       <c r="G188" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H188" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J188" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K188" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="L188" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
     </row>
     <row r="189" spans="2:12">
@@ -29318,19 +29640,19 @@
         <v>615</v>
       </c>
       <c r="G189" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H189" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="J189" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K189" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="L189" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
     </row>
     <row r="190" spans="2:12">
@@ -29347,19 +29669,19 @@
         <v>616</v>
       </c>
       <c r="G190" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H190" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J190" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K190" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="L190" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
     </row>
     <row r="191" spans="2:12">
@@ -29376,19 +29698,19 @@
         <v>617</v>
       </c>
       <c r="G191" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H191" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J191" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K191" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="L191" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
     </row>
     <row r="192" spans="2:12">
@@ -29405,19 +29727,19 @@
         <v>618</v>
       </c>
       <c r="G192" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H192" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J192" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K192" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="L192" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
     </row>
     <row r="193" spans="2:12">
@@ -29434,19 +29756,19 @@
         <v>619</v>
       </c>
       <c r="G193" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H193" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="J193" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K193" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="L193" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="194" spans="2:12">
@@ -29463,19 +29785,19 @@
         <v>620</v>
       </c>
       <c r="G194" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H194" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J194" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K194" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="L194" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
     </row>
     <row r="195" spans="2:12">
@@ -29492,19 +29814,19 @@
         <v>621</v>
       </c>
       <c r="G195" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H195" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J195" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K195" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="L195" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
     </row>
     <row r="196" spans="2:12">
@@ -29521,19 +29843,19 @@
         <v>622</v>
       </c>
       <c r="G196" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H196" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="J196" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K196" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="L196" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
     </row>
     <row r="197" spans="2:12">
@@ -29550,19 +29872,19 @@
         <v>623</v>
       </c>
       <c r="G197" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H197" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="J197" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K197" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="L197" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
     </row>
     <row r="198" spans="2:12">
@@ -29579,19 +29901,19 @@
         <v>624</v>
       </c>
       <c r="G198" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H198" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="J198" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K198" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="L198" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
     </row>
     <row r="199" spans="2:12">
@@ -29608,19 +29930,19 @@
         <v>625</v>
       </c>
       <c r="G199" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H199" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="J199" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K199" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="L199" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
     </row>
     <row r="200" spans="2:12">
@@ -29637,19 +29959,19 @@
         <v>626</v>
       </c>
       <c r="G200" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H200" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J200" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K200" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="L200" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
     </row>
     <row r="201" spans="2:12">
@@ -29666,19 +29988,19 @@
         <v>627</v>
       </c>
       <c r="G201" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H201" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J201" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K201" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="L201" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
     </row>
     <row r="202" spans="2:12">
@@ -29695,19 +30017,19 @@
         <v>628</v>
       </c>
       <c r="G202" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H202" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="J202" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K202" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="L202" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
     </row>
     <row r="203" spans="2:12">
@@ -29724,19 +30046,19 @@
         <v>629</v>
       </c>
       <c r="G203" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H203" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="J203" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K203" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="L203" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
     </row>
     <row r="204" spans="2:12">
@@ -29753,19 +30075,19 @@
         <v>630</v>
       </c>
       <c r="G204" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H204" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="J204" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K204" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="L204" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
     </row>
     <row r="205" spans="2:12">
@@ -29782,19 +30104,19 @@
         <v>631</v>
       </c>
       <c r="G205" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H205" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="J205" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K205" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="L205" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="206" spans="2:12">
@@ -29811,19 +30133,19 @@
         <v>632</v>
       </c>
       <c r="G206" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H206" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="J206" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K206" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="L206" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
     </row>
     <row r="207" spans="2:12">
@@ -29840,19 +30162,19 @@
         <v>633</v>
       </c>
       <c r="G207" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H207" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J207" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K207" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="L207" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
     </row>
     <row r="208" spans="2:12">
@@ -29869,19 +30191,19 @@
         <v>634</v>
       </c>
       <c r="G208" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H208" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J208" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K208" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="L208" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
     </row>
     <row r="209" spans="2:12">
@@ -29898,19 +30220,19 @@
         <v>635</v>
       </c>
       <c r="G209" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H209" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="J209" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K209" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="L209" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
     </row>
     <row r="210" spans="2:12">
@@ -29927,19 +30249,19 @@
         <v>636</v>
       </c>
       <c r="G210" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H210" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J210" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K210" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="L210" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
     </row>
     <row r="211" spans="2:12">
@@ -29956,19 +30278,19 @@
         <v>637</v>
       </c>
       <c r="G211" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H211" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J211" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K211" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="L211" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
     </row>
     <row r="212" spans="2:12">
@@ -29985,19 +30307,19 @@
         <v>638</v>
       </c>
       <c r="G212" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H212" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J212" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K212" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="L212" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
     </row>
     <row r="213" spans="2:12">
@@ -30014,19 +30336,19 @@
         <v>639</v>
       </c>
       <c r="G213" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H213" t="s">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="J213" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K213" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="L213" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
     </row>
     <row r="214" spans="2:12">
@@ -30043,19 +30365,19 @@
         <v>640</v>
       </c>
       <c r="G214" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H214" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="J214" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="K214" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="L214" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
     </row>
     <row r="215" spans="2:12">
@@ -30072,19 +30394,338 @@
         <v>641</v>
       </c>
       <c r="G215" t="s">
+        <v>653</v>
+      </c>
+      <c r="H215" t="s">
+        <v>656</v>
+      </c>
+      <c r="J215" t="s">
+        <v>672</v>
+      </c>
+      <c r="K215" t="s">
+        <v>877</v>
+      </c>
+      <c r="L215" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="216" spans="2:12">
+      <c r="B216" t="s">
+        <v>436</v>
+      </c>
+      <c r="C216" t="s">
         <v>642</v>
       </c>
-      <c r="H215" t="s">
+      <c r="D216" t="s">
+        <v>642</v>
+      </c>
+      <c r="F216" t="s">
+        <v>642</v>
+      </c>
+      <c r="G216" t="s">
+        <v>653</v>
+      </c>
+      <c r="H216" t="s">
+        <v>656</v>
+      </c>
+      <c r="J216" t="s">
+        <v>672</v>
+      </c>
+      <c r="K216" t="s">
+        <v>878</v>
+      </c>
+      <c r="L216" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="217" spans="2:12">
+      <c r="B217" t="s">
+        <v>436</v>
+      </c>
+      <c r="C217" t="s">
+        <v>643</v>
+      </c>
+      <c r="D217" t="s">
+        <v>643</v>
+      </c>
+      <c r="F217" t="s">
+        <v>643</v>
+      </c>
+      <c r="G217" t="s">
+        <v>653</v>
+      </c>
+      <c r="H217" t="s">
+        <v>656</v>
+      </c>
+      <c r="J217" t="s">
+        <v>672</v>
+      </c>
+      <c r="K217" t="s">
+        <v>879</v>
+      </c>
+      <c r="L217" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="218" spans="2:12">
+      <c r="B218" t="s">
+        <v>436</v>
+      </c>
+      <c r="C218" t="s">
+        <v>644</v>
+      </c>
+      <c r="D218" t="s">
+        <v>644</v>
+      </c>
+      <c r="F218" t="s">
+        <v>644</v>
+      </c>
+      <c r="G218" t="s">
+        <v>653</v>
+      </c>
+      <c r="H218" t="s">
+        <v>656</v>
+      </c>
+      <c r="J218" t="s">
+        <v>672</v>
+      </c>
+      <c r="K218" t="s">
+        <v>880</v>
+      </c>
+      <c r="L218" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="219" spans="2:12">
+      <c r="B219" t="s">
+        <v>436</v>
+      </c>
+      <c r="C219" t="s">
         <v>645</v>
       </c>
-      <c r="J215" t="s">
-        <v>660</v>
-      </c>
-      <c r="K215" t="s">
-        <v>865</v>
-      </c>
-      <c r="L215" t="s">
-        <v>865</v>
+      <c r="D219" t="s">
+        <v>645</v>
+      </c>
+      <c r="F219" t="s">
+        <v>645</v>
+      </c>
+      <c r="G219" t="s">
+        <v>653</v>
+      </c>
+      <c r="H219" t="s">
+        <v>656</v>
+      </c>
+      <c r="J219" t="s">
+        <v>672</v>
+      </c>
+      <c r="K219" t="s">
+        <v>881</v>
+      </c>
+      <c r="L219" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12">
+      <c r="B220" t="s">
+        <v>436</v>
+      </c>
+      <c r="C220" t="s">
+        <v>646</v>
+      </c>
+      <c r="D220" t="s">
+        <v>646</v>
+      </c>
+      <c r="F220" t="s">
+        <v>646</v>
+      </c>
+      <c r="G220" t="s">
+        <v>653</v>
+      </c>
+      <c r="H220" t="s">
+        <v>656</v>
+      </c>
+      <c r="J220" t="s">
+        <v>672</v>
+      </c>
+      <c r="K220" t="s">
+        <v>882</v>
+      </c>
+      <c r="L220" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="221" spans="2:12">
+      <c r="B221" t="s">
+        <v>436</v>
+      </c>
+      <c r="C221" t="s">
+        <v>647</v>
+      </c>
+      <c r="D221" t="s">
+        <v>647</v>
+      </c>
+      <c r="F221" t="s">
+        <v>647</v>
+      </c>
+      <c r="G221" t="s">
+        <v>653</v>
+      </c>
+      <c r="H221" t="s">
+        <v>656</v>
+      </c>
+      <c r="J221" t="s">
+        <v>672</v>
+      </c>
+      <c r="K221" t="s">
+        <v>883</v>
+      </c>
+      <c r="L221" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="222" spans="2:12">
+      <c r="B222" t="s">
+        <v>436</v>
+      </c>
+      <c r="C222" t="s">
+        <v>648</v>
+      </c>
+      <c r="D222" t="s">
+        <v>648</v>
+      </c>
+      <c r="F222" t="s">
+        <v>648</v>
+      </c>
+      <c r="G222" t="s">
+        <v>653</v>
+      </c>
+      <c r="H222" t="s">
+        <v>656</v>
+      </c>
+      <c r="J222" t="s">
+        <v>672</v>
+      </c>
+      <c r="K222" t="s">
+        <v>884</v>
+      </c>
+      <c r="L222" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="223" spans="2:12">
+      <c r="B223" t="s">
+        <v>436</v>
+      </c>
+      <c r="C223" t="s">
+        <v>649</v>
+      </c>
+      <c r="D223" t="s">
+        <v>649</v>
+      </c>
+      <c r="F223" t="s">
+        <v>649</v>
+      </c>
+      <c r="G223" t="s">
+        <v>653</v>
+      </c>
+      <c r="H223" t="s">
+        <v>656</v>
+      </c>
+      <c r="J223" t="s">
+        <v>672</v>
+      </c>
+      <c r="K223" t="s">
+        <v>885</v>
+      </c>
+      <c r="L223" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="224" spans="2:12">
+      <c r="B224" t="s">
+        <v>436</v>
+      </c>
+      <c r="C224" t="s">
+        <v>650</v>
+      </c>
+      <c r="D224" t="s">
+        <v>650</v>
+      </c>
+      <c r="F224" t="s">
+        <v>650</v>
+      </c>
+      <c r="G224" t="s">
+        <v>653</v>
+      </c>
+      <c r="H224" t="s">
+        <v>656</v>
+      </c>
+      <c r="J224" t="s">
+        <v>672</v>
+      </c>
+      <c r="K224" t="s">
+        <v>886</v>
+      </c>
+      <c r="L224" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="225" spans="2:12">
+      <c r="B225" t="s">
+        <v>436</v>
+      </c>
+      <c r="C225" t="s">
+        <v>651</v>
+      </c>
+      <c r="D225" t="s">
+        <v>651</v>
+      </c>
+      <c r="F225" t="s">
+        <v>651</v>
+      </c>
+      <c r="G225" t="s">
+        <v>653</v>
+      </c>
+      <c r="H225" t="s">
+        <v>656</v>
+      </c>
+      <c r="J225" t="s">
+        <v>672</v>
+      </c>
+      <c r="K225" t="s">
+        <v>887</v>
+      </c>
+      <c r="L225" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="226" spans="2:12">
+      <c r="B226" t="s">
+        <v>436</v>
+      </c>
+      <c r="C226" t="s">
+        <v>652</v>
+      </c>
+      <c r="D226" t="s">
+        <v>652</v>
+      </c>
+      <c r="F226" t="s">
+        <v>652</v>
+      </c>
+      <c r="G226" t="s">
+        <v>653</v>
+      </c>
+      <c r="H226" t="s">
+        <v>656</v>
+      </c>
+      <c r="J226" t="s">
+        <v>672</v>
+      </c>
+      <c r="K226" t="s">
+        <v>888</v>
+      </c>
+      <c r="L226" t="s">
+        <v>888</v>
       </c>
     </row>
   </sheetData>
